--- a/NoiceAndFakes/noice.xlsx
+++ b/NoiceAndFakes/noice.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="504" windowWidth="23256" windowHeight="13176"/>
+    <workbookView xWindow="0" yWindow="510" windowWidth="21840" windowHeight="13170"/>
   </bookViews>
   <sheets>
     <sheet name="noice" sheetId="6" r:id="rId1"/>
@@ -501,7 +501,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -510,9 +510,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:V209"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>20</v>
       </c>
@@ -531,7 +531,7 @@
       <c r="N1" s="13"/>
       <c r="O1" s="13"/>
     </row>
-    <row r="2" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" ht="17.45" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -541,7 +541,7 @@
       </c>
       <c r="D2">
         <f ca="1">RSQ(B3:B459,D3:D459)</f>
-        <v>0.99463213692660091</v>
+        <v>0.9946000077924162</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>2</v>
@@ -596,7 +596,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -608,11 +608,11 @@
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D66" ca="1" si="0">B3+M3</f>
-        <v>29.227899999999998</v>
+        <v>29.228200000000001</v>
       </c>
       <c r="E3" s="3">
         <f ca="1">RSQ(B3:B209,D3:D209)</f>
-        <v>0.99463213692660091</v>
+        <v>0.9946000077924162</v>
       </c>
       <c r="F3" s="5" t="e">
         <f>RSQ(B367:B459,D367:D459)</f>
@@ -629,33 +629,33 @@
       </c>
       <c r="J3">
         <f ca="1">IF(B3 &lt; 30, RANDBETWEEN(-100, 100) / 10000, RANDBETWEEN(-100,100) / 100)</f>
-        <v>6.0000000000000001E-3</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="K3">
         <f ca="1">IF(B3 &lt; 30, RANDBETWEEN(-100, 100) / 10000, RANDBETWEEN(-100,100) / 100)</f>
-        <v>7.4000000000000003E-3</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="L3">
         <v>0.5</v>
       </c>
       <c r="M3">
         <f t="shared" ref="M3:M66" ca="1" si="1">(I3+J3+K3)*L3</f>
-        <v>1.0678999999999994</v>
+        <v>1.0681999999999996</v>
       </c>
       <c r="N3">
         <f t="shared" ref="N3:N66" ca="1" si="2">((D3/B3)-1)*100</f>
-        <v>3.7922585227272654</v>
+        <v>3.7933238636363775</v>
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O66" ca="1" si="3">M3^2</f>
-        <v>1.1404104099999988</v>
+        <v>1.141051239999999</v>
       </c>
       <c r="P3">
         <f ca="1">SQRT(P110/997)</f>
-        <v>0.86667866892681156</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.86634266707658658</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -667,7 +667,7 @@
       </c>
       <c r="D4" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>18.824449999999999</v>
+        <v>18.827449999999999</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>18</v>
@@ -686,29 +686,29 @@
       </c>
       <c r="J4">
         <f t="shared" ref="J4:J67" ca="1" si="6">IF(B4 &lt; 30, RANDBETWEEN(-100, 100) / 10000, RANDBETWEEN(-100,100) / 100)</f>
-        <v>0</v>
+        <v>-3.0000000000000001E-3</v>
       </c>
       <c r="K4">
         <f t="shared" ref="K4:K67" ca="1" si="7">IF(B4 &lt; 30, RANDBETWEEN(-100, 100) / 10000, RANDBETWEEN(-100,100) / 100)</f>
-        <v>-6.3E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="L4">
         <v>0.5</v>
       </c>
       <c r="M4">
         <f t="shared" ca="1" si="1"/>
-        <v>0.25445000000000007</v>
+        <v>0.25745000000000007</v>
       </c>
       <c r="N4">
         <f t="shared" ca="1" si="2"/>
-        <v>1.3702207862143156</v>
+        <v>1.3863758750673139</v>
       </c>
       <c r="O4">
         <f t="shared" ca="1" si="3"/>
-        <v>6.4744802500000032E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>6.6280502500000033E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -720,7 +720,7 @@
       </c>
       <c r="D5" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>14.14655</v>
+        <v>14.139250000000001</v>
       </c>
       <c r="E5" s="3" t="e">
         <f>SQRT((SUM(#REF!)/169))</f>
@@ -741,29 +741,29 @@
       </c>
       <c r="J5">
         <f t="shared" ca="1" si="6"/>
-        <v>-4.7999999999999996E-3</v>
+        <v>-5.3E-3</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="7"/>
-        <v>5.1999999999999998E-3</v>
+        <v>-8.8999999999999999E-3</v>
       </c>
       <c r="L5">
         <v>0.5</v>
       </c>
       <c r="M5">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.1134499999999998</v>
+        <v>-1.1207499999999999</v>
       </c>
       <c r="N5">
         <f t="shared" ca="1" si="2"/>
-        <v>-7.2965268676277839</v>
+        <v>-7.3443643512450807</v>
       </c>
       <c r="O5">
         <f t="shared" ca="1" si="3"/>
-        <v>1.2397709024999997</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.2560805624999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -775,7 +775,7 @@
       </c>
       <c r="D6" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>7.6393699999999995</v>
+        <v>7.6318200000000003</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -790,29 +790,29 @@
       </c>
       <c r="J6">
         <f t="shared" ca="1" si="6"/>
-        <v>-4.0000000000000001E-3</v>
+        <v>-7.1000000000000004E-3</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="7"/>
-        <v>5.1000000000000004E-3</v>
+        <v>-6.8999999999999999E-3</v>
       </c>
       <c r="L6">
         <v>0.5</v>
       </c>
       <c r="M6">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.37062999999999985</v>
+        <v>-0.37817999999999985</v>
       </c>
       <c r="N6">
         <f t="shared" ca="1" si="2"/>
-        <v>-4.6270911360799083</v>
+        <v>-4.7213483146067325</v>
       </c>
       <c r="O6">
         <f t="shared" ca="1" si="3"/>
-        <v>0.13736659689999989</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.1430201123999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -824,7 +824,7 @@
       </c>
       <c r="D7" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>47.97195</v>
+        <v>47.72195</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -841,29 +841,29 @@
       </c>
       <c r="J7">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="7"/>
-        <v>0.72</v>
+        <v>-0.38</v>
       </c>
       <c r="L7">
         <v>0.5</v>
       </c>
       <c r="M7">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.0180500000000023</v>
+        <v>-1.2680500000000023</v>
       </c>
       <c r="N7">
         <f t="shared" ca="1" si="2"/>
-        <v>-2.0780771586037972</v>
+        <v>-2.588385384772407</v>
       </c>
       <c r="O7">
         <f t="shared" ca="1" si="3"/>
-        <v>1.0364258025000048</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.607950802500006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -875,7 +875,7 @@
       </c>
       <c r="D8" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>43.211599999999997</v>
+        <v>43.276600000000002</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1">
@@ -892,29 +892,29 @@
       </c>
       <c r="J8">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.54</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.47</v>
+        <v>-0.88</v>
       </c>
       <c r="L8">
         <v>0.5</v>
       </c>
       <c r="M8">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.3683999999999985</v>
+        <v>-1.3033999999999986</v>
       </c>
       <c r="N8">
         <f t="shared" ca="1" si="2"/>
-        <v>-3.0695379093764075</v>
+        <v>-2.9237326155226451</v>
       </c>
       <c r="O8">
         <f t="shared" ca="1" si="3"/>
-        <v>1.8725185599999958</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.6988515599999963</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -926,7 +926,7 @@
       </c>
       <c r="D9" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>32.792200000000001</v>
+        <v>33.447200000000002</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1">
@@ -945,29 +945,29 @@
       </c>
       <c r="J9">
         <f t="shared" ca="1" si="6"/>
-        <v>0.16</v>
+        <v>1</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="7"/>
-        <v>0.23</v>
+        <v>0.7</v>
       </c>
       <c r="L9">
         <v>0.5</v>
       </c>
       <c r="M9">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.3277999999999983</v>
+        <v>-0.6727999999999984</v>
       </c>
       <c r="N9">
         <f t="shared" ca="1" si="2"/>
-        <v>-3.8915592028135881</v>
+        <v>-1.9718640093786544</v>
       </c>
       <c r="O9">
         <f t="shared" ca="1" si="3"/>
-        <v>1.7630528399999956</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.45265983999999787</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -979,7 +979,7 @@
       </c>
       <c r="D10" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>15.129850000000001</v>
+        <v>15.133100000000001</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1">
@@ -996,29 +996,29 @@
       </c>
       <c r="J10">
         <f t="shared" ca="1" si="6"/>
-        <v>5.9999999999999995E-4</v>
+        <v>3.3999999999999998E-3</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="7"/>
-        <v>1.8E-3</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="L10">
         <v>0.5</v>
       </c>
       <c r="M10">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.11014999999999985</v>
+        <v>-0.10689999999999984</v>
       </c>
       <c r="N10">
         <f t="shared" ca="1" si="2"/>
-        <v>-0.72276902887138395</v>
+        <v>-0.70144356955380571</v>
       </c>
       <c r="O10">
         <f t="shared" ca="1" si="3"/>
-        <v>1.2133022499999965E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.1427609999999967E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="D11" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>37.410000000000004</v>
+        <v>38.24</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1">
@@ -1049,29 +1049,29 @@
       </c>
       <c r="J11">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.3</v>
+        <v>0.27</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.37</v>
+        <v>0.72</v>
       </c>
       <c r="L11">
         <v>0.5</v>
       </c>
       <c r="M11">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.58999999999999897</v>
+        <v>0.24000000000000099</v>
       </c>
       <c r="N11">
         <f t="shared" ca="1" si="2"/>
-        <v>-1.552631578947361</v>
+        <v>0.63157894736842746</v>
       </c>
       <c r="O11">
         <f t="shared" ca="1" si="3"/>
-        <v>0.3480999999999988</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+        <v>5.7600000000000477E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D12" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>36.013850000000005</v>
+        <v>35.813850000000002</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1">
@@ -1102,29 +1102,29 @@
       </c>
       <c r="J12">
         <f t="shared" ca="1" si="6"/>
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.02</v>
+        <v>-0.31</v>
       </c>
       <c r="L12">
         <v>0.5</v>
       </c>
       <c r="M12">
         <f t="shared" ca="1" si="1"/>
-        <v>1.3850000000001592E-2</v>
+        <v>-0.1861499999999984</v>
       </c>
       <c r="N12">
         <f t="shared" ca="1" si="2"/>
-        <v>3.8472222222241115E-2</v>
+        <v>-0.51708333333332357</v>
       </c>
       <c r="O12">
         <f t="shared" ca="1" si="3"/>
-        <v>1.918225000000441E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3.4651822499999402E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="D13" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>12.1867</v>
+        <v>12.185</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1">
@@ -1153,29 +1153,29 @@
       </c>
       <c r="J13">
         <f t="shared" ca="1" si="6"/>
-        <v>-3.8999999999999998E-3</v>
+        <v>-6.7999999999999996E-3</v>
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="7"/>
-        <v>2.9999999999999997E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="L13">
         <v>0.5</v>
       </c>
       <c r="M13">
         <f t="shared" ca="1" si="1"/>
-        <v>0.18670000000000034</v>
+        <v>0.18500000000000036</v>
       </c>
       <c r="N13">
         <f t="shared" ca="1" si="2"/>
-        <v>1.5558333333333341</v>
+        <v>1.5416666666666634</v>
       </c>
       <c r="O13">
         <f t="shared" ca="1" si="3"/>
-        <v>3.4856890000000126E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3.422500000000013E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D14" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>45.366349999999997</v>
+        <v>45.481349999999999</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -1202,29 +1202,29 @@
       </c>
       <c r="J14">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.54</v>
+        <v>0.18</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="7"/>
-        <v>0.39</v>
+        <v>-0.1</v>
       </c>
       <c r="L14">
         <v>0.5</v>
       </c>
       <c r="M14">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.63365000000000005</v>
+        <v>-0.51865000000000017</v>
       </c>
       <c r="N14">
         <f t="shared" ca="1" si="2"/>
-        <v>-1.3775000000000093</v>
+        <v>-1.1275000000000035</v>
       </c>
       <c r="O14">
         <f t="shared" ca="1" si="3"/>
-        <v>0.40151232250000007</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.26899782250000015</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D15" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>40.983249999999998</v>
+        <v>42.603250000000003</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -1251,29 +1251,29 @@
       </c>
       <c r="J15">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.95</v>
+        <v>0.67</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.92</v>
+        <v>0.7</v>
       </c>
       <c r="L15">
         <v>0.5</v>
       </c>
       <c r="M15">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.5167499999999996</v>
+        <v>1.1032500000000005</v>
       </c>
       <c r="N15">
         <f t="shared" ca="1" si="2"/>
-        <v>-1.2451807228915701</v>
+        <v>2.6584337349397691</v>
       </c>
       <c r="O15">
         <f t="shared" ca="1" si="3"/>
-        <v>0.26703056249999957</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.217160562500001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D16" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>36.356450000000002</v>
+        <v>36.846450000000004</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -1300,29 +1300,29 @@
       </c>
       <c r="J16">
         <f t="shared" ca="1" si="6"/>
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.4</v>
+        <v>0.49</v>
       </c>
       <c r="L16">
         <v>0.5</v>
       </c>
       <c r="M16">
         <f t="shared" ca="1" si="1"/>
-        <v>0.15644999999999937</v>
+        <v>0.64644999999999941</v>
       </c>
       <c r="N16">
         <f t="shared" ca="1" si="2"/>
-        <v>0.43218232044199834</v>
+        <v>1.7857734806629777</v>
       </c>
       <c r="O16">
         <f t="shared" ca="1" si="3"/>
-        <v>2.4476602499999802E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.41789760249999924</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="D17" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>48.007899999999999</v>
+        <v>48.497900000000001</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -1349,29 +1349,29 @@
       </c>
       <c r="J17">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.94</v>
+        <v>-0.01</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.91</v>
+        <v>-0.86</v>
       </c>
       <c r="L17">
         <v>0.5</v>
       </c>
       <c r="M17">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.9921</v>
+        <v>-1.5020999999999998</v>
       </c>
       <c r="N17">
         <f t="shared" ca="1" si="2"/>
-        <v>-3.9842000000000044</v>
+        <v>-3.0042000000000013</v>
       </c>
       <c r="O17">
         <f t="shared" ca="1" si="3"/>
-        <v>3.9684624099999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2.2563044099999994</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D18" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>40.144100000000002</v>
+        <v>39.829099999999997</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -1398,29 +1398,29 @@
       </c>
       <c r="J18">
         <f t="shared" ca="1" si="6"/>
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="7"/>
-        <v>0.28000000000000003</v>
+        <v>-0.31</v>
       </c>
       <c r="L18">
         <v>0.5</v>
       </c>
       <c r="M18">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.8558999999999997</v>
+        <v>-2.1708999999999996</v>
       </c>
       <c r="N18">
         <f t="shared" ca="1" si="2"/>
-        <v>-4.4188095238095197</v>
+        <v>-5.1688095238095366</v>
       </c>
       <c r="O18">
         <f t="shared" ca="1" si="3"/>
-        <v>3.4443648099999988</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>4.7128068099999982</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D19" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>20.962500000000002</v>
+        <v>20.965150000000001</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -1447,29 +1447,29 @@
       </c>
       <c r="J19">
         <f t="shared" ca="1" si="6"/>
-        <v>6.3E-3</v>
+        <v>8.2000000000000007E-3</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="7"/>
-        <v>-7.6E-3</v>
+        <v>-4.1999999999999997E-3</v>
       </c>
       <c r="L19">
         <v>0.5</v>
       </c>
       <c r="M19">
         <f t="shared" ca="1" si="1"/>
-        <v>-3.7499999999999381E-2</v>
+        <v>-3.4849999999999381E-2</v>
       </c>
       <c r="N19">
         <f t="shared" ca="1" si="2"/>
-        <v>-0.17857142857141683</v>
+        <v>-0.16595238095237219</v>
       </c>
       <c r="O19">
         <f t="shared" ca="1" si="3"/>
-        <v>1.4062499999999535E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.2145224999999568E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D20" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>32.884299999999996</v>
+        <v>32.924299999999995</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1496,29 +1496,29 @@
       </c>
       <c r="J20">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.96</v>
+        <v>-0.26</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="7"/>
-        <v>0.02</v>
+        <v>-0.6</v>
       </c>
       <c r="L20">
         <v>0.5</v>
       </c>
       <c r="M20">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.11570000000000148</v>
+        <v>-7.5700000000001488E-2</v>
       </c>
       <c r="N20">
         <f t="shared" ca="1" si="2"/>
-        <v>-0.35060606060607347</v>
+        <v>-0.22939393939395147</v>
       </c>
       <c r="O20">
         <f t="shared" ca="1" si="3"/>
-        <v>1.3386490000000343E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5.7304900000002251E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D21" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>29.578800000000001</v>
+        <v>29.566649999999999</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
@@ -1545,29 +1545,29 @@
       </c>
       <c r="J21">
         <f t="shared" ca="1" si="6"/>
-        <v>7.0000000000000001E-3</v>
+        <v>-7.9000000000000008E-3</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="7"/>
-        <v>1E-4</v>
+        <v>-9.2999999999999992E-3</v>
       </c>
       <c r="L21">
         <v>0.5</v>
       </c>
       <c r="M21">
         <f t="shared" ca="1" si="1"/>
-        <v>0.57880000000000043</v>
+        <v>0.56665000000000043</v>
       </c>
       <c r="N21">
         <f t="shared" ca="1" si="2"/>
-        <v>1.9958620689655149</v>
+        <v>1.953965517241385</v>
       </c>
       <c r="O21">
         <f t="shared" ca="1" si="3"/>
-        <v>0.33500944000000049</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.32109222250000047</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="D22" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>12.86205</v>
+        <v>12.859500000000001</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -1594,29 +1594,29 @@
       </c>
       <c r="J22">
         <f t="shared" ca="1" si="6"/>
-        <v>4.4000000000000003E-3</v>
+        <v>5.1000000000000004E-3</v>
       </c>
       <c r="K22">
         <f t="shared" ca="1" si="7"/>
-        <v>4.5999999999999999E-3</v>
+        <v>-1.1999999999999999E-3</v>
       </c>
       <c r="L22">
         <v>0.5</v>
       </c>
       <c r="M22">
         <f t="shared" ca="1" si="1"/>
-        <v>0.36204999999999982</v>
+        <v>0.35949999999999982</v>
       </c>
       <c r="N22">
         <f t="shared" ca="1" si="2"/>
-        <v>2.896399999999999</v>
+        <v>2.8760000000000119</v>
       </c>
       <c r="O22">
         <f t="shared" ca="1" si="3"/>
-        <v>0.13108020249999985</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.12924024999999986</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D23" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>33.827300000000001</v>
+        <v>33.392299999999999</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -1643,29 +1643,29 @@
       </c>
       <c r="J23">
         <f t="shared" ca="1" si="6"/>
-        <v>0.35</v>
+        <v>-0.26</v>
       </c>
       <c r="K23">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="L23">
         <v>0.5</v>
       </c>
       <c r="M23">
         <f t="shared" ca="1" si="1"/>
-        <v>1.8273000000000004</v>
+        <v>1.3923000000000005</v>
       </c>
       <c r="N23">
         <f t="shared" ca="1" si="2"/>
-        <v>5.7103125000000032</v>
+        <v>4.3509374999999961</v>
       </c>
       <c r="O23">
         <f t="shared" ca="1" si="3"/>
-        <v>3.3390252900000013</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.9384992900000015</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="D24" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>30.837299999999999</v>
+        <v>30.836849999999998</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
@@ -1692,29 +1692,29 @@
       </c>
       <c r="J24">
         <f t="shared" ca="1" si="6"/>
-        <v>1.2999999999999999E-3</v>
+        <v>-1.9E-3</v>
       </c>
       <c r="K24">
         <f t="shared" ca="1" si="7"/>
-        <v>4.8999999999999998E-3</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="L24">
         <v>0.5</v>
       </c>
       <c r="M24">
         <f t="shared" ca="1" si="1"/>
-        <v>1.3372999999999993</v>
+        <v>1.3368499999999992</v>
       </c>
       <c r="N24">
         <f t="shared" ca="1" si="2"/>
-        <v>4.5332203389830461</v>
+        <v>4.5316949152542252</v>
       </c>
       <c r="O24">
         <f t="shared" ca="1" si="3"/>
-        <v>1.7883712899999979</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.7871679224999979</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="D25" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>28.728000000000002</v>
+        <v>28.725750000000001</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -1741,29 +1741,29 @@
       </c>
       <c r="J25">
         <f t="shared" ca="1" si="6"/>
-        <v>-3.8999999999999998E-3</v>
+        <v>-2.3E-3</v>
       </c>
       <c r="K25">
         <f t="shared" ca="1" si="7"/>
-        <v>1.6000000000000001E-3</v>
+        <v>-4.4999999999999997E-3</v>
       </c>
       <c r="L25">
         <v>0.5</v>
       </c>
       <c r="M25">
         <f t="shared" ca="1" si="1"/>
-        <v>0.22800000000000062</v>
+        <v>0.22575000000000062</v>
       </c>
       <c r="N25">
         <f t="shared" ca="1" si="2"/>
-        <v>0.80000000000000071</v>
+        <v>0.79210526315789398</v>
       </c>
       <c r="O25">
         <f t="shared" ca="1" si="3"/>
-        <v>5.198400000000028E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5.0963062500000281E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D26" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>35.159500000000001</v>
+        <v>35.474499999999999</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -1790,29 +1790,29 @@
       </c>
       <c r="J26">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.28000000000000003</v>
+        <v>-0.11</v>
       </c>
       <c r="K26">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.67</v>
+        <v>-0.21</v>
       </c>
       <c r="L26">
         <v>0.5</v>
       </c>
       <c r="M26">
         <f t="shared" ca="1" si="1"/>
-        <v>0.15949999999999914</v>
+        <v>0.47449999999999914</v>
       </c>
       <c r="N26">
         <f t="shared" ca="1" si="2"/>
-        <v>0.45571428571429262</v>
+        <v>1.3557142857142823</v>
       </c>
       <c r="O26">
         <f t="shared" ca="1" si="3"/>
-        <v>2.5440249999999727E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.22515024999999919</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="D27" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>28.743749999999999</v>
+        <v>28.75835</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -1839,29 +1839,29 @@
       </c>
       <c r="J27">
         <f t="shared" ca="1" si="6"/>
-        <v>-8.3999999999999995E-3</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="K27">
         <f t="shared" ca="1" si="7"/>
-        <v>-6.3E-3</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="L27">
         <v>0.5</v>
       </c>
       <c r="M27">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.25625000000000075</v>
+        <v>-0.24165000000000081</v>
       </c>
       <c r="N27">
         <f t="shared" ca="1" si="2"/>
-        <v>-0.88362068965517349</v>
+        <v>-0.83327586206896065</v>
       </c>
       <c r="O27">
         <f t="shared" ca="1" si="3"/>
-        <v>6.5664062500000384E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5.8394722500000391E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="D28" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>10.80875</v>
+        <v>10.814249999999999</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
@@ -1888,29 +1888,29 @@
       </c>
       <c r="J28">
         <f t="shared" ca="1" si="6"/>
-        <v>3.3999999999999998E-3</v>
+        <v>7.7000000000000002E-3</v>
       </c>
       <c r="K28">
         <f t="shared" ca="1" si="7"/>
-        <v>-9.1999999999999998E-3</v>
+        <v>-2.5000000000000001E-3</v>
       </c>
       <c r="L28">
         <v>0.5</v>
       </c>
       <c r="M28">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.19124999999999978</v>
+        <v>-0.1857499999999998</v>
       </c>
       <c r="N28">
         <f t="shared" ca="1" si="2"/>
-        <v>-1.73863636363637</v>
+        <v>-1.6886363636363644</v>
       </c>
       <c r="O28">
         <f t="shared" ca="1" si="3"/>
-        <v>3.6576562499999916E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3.4503062499999924E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D29" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>37.824350000000003</v>
+        <v>37.544350000000001</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
@@ -1937,29 +1937,29 @@
       </c>
       <c r="J29">
         <f t="shared" ca="1" si="6"/>
-        <v>0.23</v>
+        <v>-0.5</v>
       </c>
       <c r="K29">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.19</v>
+        <v>-0.02</v>
       </c>
       <c r="L29">
         <v>0.5</v>
       </c>
       <c r="M29">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.17565000000000053</v>
+        <v>-0.45565000000000055</v>
       </c>
       <c r="N29">
         <f t="shared" ca="1" si="2"/>
-        <v>-0.46223684210525695</v>
+        <v>-1.1990789473684149</v>
       </c>
       <c r="O29">
         <f t="shared" ca="1" si="3"/>
-        <v>3.0852922500000185E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.20761692250000049</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="D30" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>34.980850000000004</v>
+        <v>34.915849999999999</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -1986,29 +1986,29 @@
       </c>
       <c r="J30">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.49</v>
+        <v>-0.55000000000000004</v>
       </c>
       <c r="K30">
         <f t="shared" ca="1" si="7"/>
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="L30">
         <v>0.5</v>
       </c>
       <c r="M30">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.9149999999998495E-2</v>
+        <v>-8.4149999999998518E-2</v>
       </c>
       <c r="N30">
         <f t="shared" ca="1" si="2"/>
-        <v>-5.4714285714274613E-2</v>
+        <v>-0.24042857142857477</v>
       </c>
       <c r="O30">
         <f t="shared" ca="1" si="3"/>
-        <v>3.6672249999994232E-4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>7.0812224999997507E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="D31" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>11.97035</v>
+        <v>11.977</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
@@ -2035,29 +2035,29 @@
       </c>
       <c r="J31">
         <f t="shared" ca="1" si="6"/>
-        <v>2.7000000000000001E-3</v>
+        <v>-2.2000000000000001E-3</v>
       </c>
       <c r="K31">
         <f t="shared" ca="1" si="7"/>
-        <v>-8.3999999999999995E-3</v>
+        <v>9.7999999999999997E-3</v>
       </c>
       <c r="L31">
         <v>0.5</v>
       </c>
       <c r="M31">
         <f t="shared" ca="1" si="1"/>
-        <v>-2.9649999999999711E-2</v>
+        <v>-2.2999999999999715E-2</v>
       </c>
       <c r="N31">
         <f t="shared" ca="1" si="2"/>
-        <v>-0.2470833333333311</v>
+        <v>-0.19166666666666776</v>
       </c>
       <c r="O31">
         <f t="shared" ca="1" si="3"/>
-        <v>8.7912249999998291E-4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5.2899999999998695E-4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="D32" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>28.144549999999999</v>
+        <v>28.1432</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
@@ -2084,29 +2084,29 @@
       </c>
       <c r="J32">
         <f t="shared" ca="1" si="6"/>
-        <v>-2E-3</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="K32">
         <f t="shared" ca="1" si="7"/>
-        <v>5.8999999999999999E-3</v>
+        <v>-4.4999999999999997E-3</v>
       </c>
       <c r="L32">
         <v>0.5</v>
       </c>
       <c r="M32">
         <f t="shared" ca="1" si="1"/>
-        <v>0.14454999999999985</v>
+        <v>0.14319999999999983</v>
       </c>
       <c r="N32">
         <f t="shared" ca="1" si="2"/>
-        <v>0.51624999999999588</v>
+        <v>0.51142857142856268</v>
       </c>
       <c r="O32">
         <f t="shared" ca="1" si="3"/>
-        <v>2.0894702499999956E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2.050623999999995E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D33" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>27.051349999999999</v>
+        <v>27.042750000000002</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -2133,29 +2133,29 @@
       </c>
       <c r="J33">
         <f t="shared" ca="1" si="6"/>
-        <v>3.3E-3</v>
+        <v>-4.4000000000000003E-3</v>
       </c>
       <c r="K33">
         <f t="shared" ca="1" si="7"/>
-        <v>3.5000000000000001E-3</v>
+        <v>-6.0000000000000001E-3</v>
       </c>
       <c r="L33">
         <v>0.5</v>
       </c>
       <c r="M33">
         <f t="shared" ca="1" si="1"/>
-        <v>5.1350000000000159E-2</v>
+        <v>4.2750000000000156E-2</v>
       </c>
       <c r="N33">
         <f t="shared" ca="1" si="2"/>
-        <v>0.19018518518518768</v>
+        <v>0.1583333333333492</v>
       </c>
       <c r="O33">
         <f t="shared" ca="1" si="3"/>
-        <v>2.6368225000000163E-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1.8275625000000134E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="D34" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>21.403099999999998</v>
+        <v>21.4117</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
@@ -2182,29 +2182,29 @@
       </c>
       <c r="J34">
         <f t="shared" ca="1" si="6"/>
-        <v>5.0000000000000001E-4</v>
+        <v>6.1000000000000004E-3</v>
       </c>
       <c r="K34">
         <f t="shared" ca="1" si="7"/>
-        <v>-7.4999999999999997E-3</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="L34">
         <v>0.5</v>
       </c>
       <c r="M34">
         <f t="shared" ca="1" si="1"/>
-        <v>0.40309999999999918</v>
+        <v>0.41169999999999918</v>
       </c>
       <c r="N34">
         <f t="shared" ca="1" si="2"/>
-        <v>1.9195238095238043</v>
+        <v>1.9604761904761903</v>
       </c>
       <c r="O34">
         <f t="shared" ca="1" si="3"/>
-        <v>0.16248960999999934</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.16949688999999932</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="D35" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>82.830950000000001</v>
+        <v>82.41095</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
@@ -2231,29 +2231,29 @@
       </c>
       <c r="J35">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.59</v>
+        <v>-0.5</v>
       </c>
       <c r="K35">
         <f t="shared" ca="1" si="7"/>
-        <v>0.56000000000000005</v>
+        <v>-0.37</v>
       </c>
       <c r="L35">
         <v>0.5</v>
       </c>
       <c r="M35">
         <f t="shared" ca="1" si="1"/>
-        <v>0.36095000000000316</v>
+        <v>-5.9049999999996883E-2</v>
       </c>
       <c r="N35">
         <f t="shared" ca="1" si="2"/>
-        <v>0.43767430580816669</v>
+        <v>-7.1601794591968915E-2</v>
       </c>
       <c r="O35">
         <f t="shared" ca="1" si="3"/>
-        <v>0.13028490250000227</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3.486902499999632E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="D36" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>22.468150000000001</v>
+        <v>22.463950000000001</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
@@ -2280,29 +2280,29 @@
       </c>
       <c r="J36">
         <f t="shared" ca="1" si="6"/>
-        <v>3.8E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="K36">
         <f t="shared" ca="1" si="7"/>
-        <v>8.9999999999999993E-3</v>
+        <v>-3.0999999999999999E-3</v>
       </c>
       <c r="L36">
         <v>0.5</v>
       </c>
       <c r="M36">
         <f t="shared" ca="1" si="1"/>
-        <v>0.43814999999999921</v>
+        <v>0.43394999999999917</v>
       </c>
       <c r="N36">
         <f t="shared" ca="1" si="2"/>
-        <v>1.9888788016341419</v>
+        <v>1.9698138901497853</v>
       </c>
       <c r="O36">
         <f t="shared" ca="1" si="3"/>
-        <v>0.1919754224999993</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.18831260249999929</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D37" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>84.512699999999995</v>
+        <v>83.612700000000004</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -2329,29 +2329,29 @@
       </c>
       <c r="J37">
         <f t="shared" ca="1" si="6"/>
-        <v>0.18</v>
+        <v>-0.41</v>
       </c>
       <c r="K37">
         <f t="shared" ca="1" si="7"/>
-        <v>0.31</v>
+        <v>-0.9</v>
       </c>
       <c r="L37">
         <v>0.5</v>
       </c>
       <c r="M37">
         <f t="shared" ca="1" si="1"/>
-        <v>0.37269999999999726</v>
+        <v>-0.52730000000000277</v>
       </c>
       <c r="N37">
         <f t="shared" ca="1" si="2"/>
-        <v>0.44295222248633692</v>
+        <v>-0.62669360589493461</v>
       </c>
       <c r="O37">
         <f t="shared" ca="1" si="3"/>
-        <v>0.13890528999999796</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0.27804529000000294</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="D38" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>69.944050000000004</v>
+        <v>69.064049999999995</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -2378,29 +2378,29 @@
       </c>
       <c r="J38">
         <f t="shared" ca="1" si="6"/>
-        <v>0.7</v>
+        <v>-0.82</v>
       </c>
       <c r="K38">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.15</v>
+        <v>-0.39</v>
       </c>
       <c r="L38">
         <v>0.5</v>
       </c>
       <c r="M38">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95405000000000384</v>
+        <v>7.4050000000003724E-2</v>
       </c>
       <c r="N38">
         <f t="shared" ca="1" si="2"/>
-        <v>1.3828815770401626</v>
+        <v>0.10733439628931585</v>
       </c>
       <c r="O38">
         <f t="shared" ca="1" si="3"/>
-        <v>0.91021140250000732</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5.4834025000005514E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="D39" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>75.205449999999999</v>
+        <v>75.540449999999993</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -2427,29 +2427,29 @@
       </c>
       <c r="J39">
         <f t="shared" ca="1" si="6"/>
-        <v>0.47</v>
+        <v>-0.06</v>
       </c>
       <c r="K39">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.47</v>
+        <v>0.73</v>
       </c>
       <c r="L39">
         <v>0.5</v>
       </c>
       <c r="M39">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.4145500000000055</v>
+        <v>-1.0795500000000056</v>
       </c>
       <c r="N39">
         <f t="shared" ca="1" si="2"/>
-        <v>-1.8461889845993285</v>
+        <v>-1.4089663273296971</v>
       </c>
       <c r="O39">
         <f t="shared" ca="1" si="3"/>
-        <v>2.0009517025000156</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.165428202500012</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="D40" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>86.225799999999992</v>
+        <v>86.370800000000003</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
@@ -2476,29 +2476,29 @@
       </c>
       <c r="J40">
         <f t="shared" ca="1" si="6"/>
-        <v>0.38</v>
+        <v>0.83</v>
       </c>
       <c r="K40">
         <f t="shared" ca="1" si="7"/>
-        <v>7.0000000000000007E-2</v>
+        <v>-0.09</v>
       </c>
       <c r="L40">
         <v>0.5</v>
       </c>
       <c r="M40">
         <f t="shared" ca="1" si="1"/>
-        <v>1.0158000000000043</v>
+        <v>1.1608000000000045</v>
       </c>
       <c r="N40">
         <f t="shared" ca="1" si="2"/>
-        <v>1.192113601689937</v>
+        <v>1.3622814223682722</v>
       </c>
       <c r="O40">
         <f t="shared" ca="1" si="3"/>
-        <v>1.0318496400000086</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.3474566400000105</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="D41" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>76.744050000000001</v>
+        <v>76.899050000000003</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
@@ -2525,29 +2525,29 @@
       </c>
       <c r="J41">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.4</v>
+        <v>-0.87</v>
       </c>
       <c r="K41">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.76</v>
+        <v>0.02</v>
       </c>
       <c r="L41">
         <v>0.5</v>
       </c>
       <c r="M41">
         <f t="shared" ca="1" si="1"/>
-        <v>-2.3759500000000049</v>
+        <v>-2.2209500000000051</v>
       </c>
       <c r="N41">
         <f t="shared" ca="1" si="2"/>
-        <v>-3.0029701718908064</v>
+        <v>-2.8070652173913024</v>
       </c>
       <c r="O41">
         <f t="shared" ca="1" si="3"/>
-        <v>5.6451384025000229</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4.9326189025000229</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -2574,18 +2574,18 @@
       </c>
       <c r="J42">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.92</v>
+        <v>-0.82</v>
       </c>
       <c r="K42">
         <f t="shared" ca="1" si="7"/>
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="L42">
         <v>0.5</v>
       </c>
       <c r="M42">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.5924000000000007</v>
+        <v>-0.59240000000000059</v>
       </c>
       <c r="N42">
         <f t="shared" ca="1" si="2"/>
@@ -2593,10 +2593,10 @@
       </c>
       <c r="O42">
         <f t="shared" ca="1" si="3"/>
-        <v>0.35093776000000082</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.35093776000000071</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="D43" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>47.20955</v>
+        <v>47.159549999999996</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
@@ -2623,29 +2623,29 @@
       </c>
       <c r="J43">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.61</v>
+        <v>0.51</v>
       </c>
       <c r="K43">
         <f t="shared" ca="1" si="7"/>
-        <v>0.63</v>
+        <v>-0.59</v>
       </c>
       <c r="L43">
         <v>0.5</v>
       </c>
       <c r="M43">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.180450000000002</v>
+        <v>-0.23045000000000199</v>
       </c>
       <c r="N43">
         <f t="shared" ca="1" si="2"/>
-        <v>-0.38077653513399756</v>
+        <v>-0.48628402616587296</v>
       </c>
       <c r="O43">
         <f t="shared" ca="1" si="3"/>
-        <v>3.256220250000072E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+        <v>5.3107202500000915E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="D44" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>20.88815</v>
+        <v>20.8886</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
@@ -2672,29 +2672,29 @@
       </c>
       <c r="J44">
         <f t="shared" ca="1" si="6"/>
-        <v>-1.8E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="K44">
         <f t="shared" ca="1" si="7"/>
-        <v>8.3000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="L44">
         <v>0.5</v>
       </c>
       <c r="M44">
         <f t="shared" ca="1" si="1"/>
-        <v>2.0681499999999997</v>
+        <v>2.0686</v>
       </c>
       <c r="N44">
         <f t="shared" ca="1" si="2"/>
-        <v>10.989107332624858</v>
+        <v>10.991498405951106</v>
       </c>
       <c r="O44">
         <f t="shared" ca="1" si="3"/>
-        <v>4.277244422499999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4.2791059599999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="D45" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>86.390500000000003</v>
+        <v>86.275500000000008</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -2721,29 +2721,29 @@
       </c>
       <c r="J45">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.35</v>
+        <v>-0.99</v>
       </c>
       <c r="K45">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.7</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="L45">
         <v>0.5</v>
       </c>
       <c r="M45">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.2194999999999978</v>
+        <v>-1.334499999999998</v>
       </c>
       <c r="N45">
         <f t="shared" ca="1" si="2"/>
-        <v>-1.3919643876269761</v>
+        <v>-1.5232279420157369</v>
       </c>
       <c r="O45">
         <f t="shared" ca="1" si="3"/>
-        <v>1.4871802499999947</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.7808902499999948</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="D46" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>70.507750000000001</v>
+        <v>71.112749999999991</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -2770,29 +2770,29 @@
       </c>
       <c r="J46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="K46">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.94</v>
+        <v>0.32</v>
       </c>
       <c r="L46">
         <v>0.5</v>
       </c>
       <c r="M46">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5677499999999991</v>
+        <v>2.1727499999999993</v>
       </c>
       <c r="N46">
         <f t="shared" ca="1" si="2"/>
-        <v>2.2740789091963975</v>
+        <v>3.1516536118363803</v>
       </c>
       <c r="O46">
         <f t="shared" ca="1" si="3"/>
-        <v>2.4578400624999972</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4.720842562499997</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="D47" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>89.715499999999992</v>
+        <v>89.1905</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -2819,29 +2819,29 @@
       </c>
       <c r="J47">
         <f t="shared" ca="1" si="6"/>
-        <v>0.04</v>
+        <v>-0.54</v>
       </c>
       <c r="K47">
         <f t="shared" ca="1" si="7"/>
-        <v>0.03</v>
+        <v>-0.44</v>
       </c>
       <c r="L47">
         <v>0.5</v>
       </c>
       <c r="M47">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.88449999999999929</v>
+        <v>-1.4094999999999993</v>
       </c>
       <c r="N47">
         <f t="shared" ca="1" si="2"/>
-        <v>-0.97626931567329489</v>
+        <v>-1.5557395143487751</v>
       </c>
       <c r="O47">
         <f t="shared" ca="1" si="3"/>
-        <v>0.78234024999999874</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.9866902499999981</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="D48" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>75.282499999999999</v>
+        <v>77.102499999999992</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -2868,29 +2868,29 @@
       </c>
       <c r="J48">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.91</v>
+        <v>0.9</v>
       </c>
       <c r="K48">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.93</v>
+        <v>0.9</v>
       </c>
       <c r="L48">
         <v>0.5</v>
       </c>
       <c r="M48">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.42750000000000032</v>
+        <v>1.3924999999999996</v>
       </c>
       <c r="N48">
         <f t="shared" ca="1" si="2"/>
-        <v>-0.56465460309073068</v>
+        <v>1.8392550521727724</v>
       </c>
       <c r="O48">
         <f t="shared" ca="1" si="3"/>
-        <v>0.18275625000000029</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.939056249999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="D49" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>51.116</v>
+        <v>50.411000000000001</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -2917,29 +2917,29 @@
       </c>
       <c r="J49">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.78</v>
+        <v>-0.77</v>
       </c>
       <c r="K49">
         <f t="shared" ca="1" si="7"/>
-        <v>0.7</v>
+        <v>-0.72</v>
       </c>
       <c r="L49">
         <v>0.5</v>
       </c>
       <c r="M49">
         <f t="shared" ca="1" si="1"/>
-        <v>-3.9999999999986713E-3</v>
+        <v>-0.70899999999999863</v>
       </c>
       <c r="N49">
         <f t="shared" ca="1" si="2"/>
-        <v>-7.8247261345754104E-3</v>
+        <v>-1.3869327073552373</v>
       </c>
       <c r="O49">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5999999999989371E-5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.50268099999999805</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="D50" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>76.977499999999992</v>
+        <v>76.827500000000001</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -2966,29 +2966,29 @@
       </c>
       <c r="J50">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.48</v>
+        <v>-0.43</v>
       </c>
       <c r="K50">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.48</v>
+        <v>-0.83</v>
       </c>
       <c r="L50">
         <v>0.5</v>
       </c>
       <c r="M50">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.2425000000000028</v>
+        <v>-1.3925000000000027</v>
       </c>
       <c r="N50">
         <f t="shared" ca="1" si="2"/>
-        <v>-1.5884684223983703</v>
+        <v>-1.7802352339555072</v>
       </c>
       <c r="O50">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5438062500000069</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.9390562500000077</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="D51" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>26.356100000000001</v>
+        <v>26.353200000000001</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -3015,29 +3015,29 @@
       </c>
       <c r="J51">
         <f t="shared" ca="1" si="6"/>
-        <v>7.4000000000000003E-3</v>
+        <v>6.6E-3</v>
       </c>
       <c r="K51">
         <f t="shared" ca="1" si="7"/>
-        <v>8.2000000000000007E-3</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="L51">
         <v>0.5</v>
       </c>
       <c r="M51">
         <f t="shared" ca="1" si="1"/>
-        <v>0.63610000000000122</v>
+        <v>0.63320000000000121</v>
       </c>
       <c r="N51">
         <f t="shared" ca="1" si="2"/>
-        <v>2.4731726283048205</v>
+        <v>2.4618973561430835</v>
       </c>
       <c r="O51">
         <f t="shared" ca="1" si="3"/>
-        <v>0.40462321000000157</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.4009422400000015</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="D52" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>96.150800000000004</v>
+        <v>95.140799999999999</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -3064,29 +3064,29 @@
       </c>
       <c r="J52">
         <f t="shared" ca="1" si="6"/>
-        <v>0.24</v>
+        <v>-0.92</v>
       </c>
       <c r="K52">
         <f t="shared" ca="1" si="7"/>
-        <v>0.1</v>
+        <v>-0.76</v>
       </c>
       <c r="L52">
         <v>0.5</v>
       </c>
       <c r="M52">
         <f t="shared" ca="1" si="1"/>
-        <v>0.35080000000000494</v>
+        <v>-0.65919999999999512</v>
       </c>
       <c r="N52">
         <f t="shared" ca="1" si="2"/>
-        <v>0.36617954070981007</v>
+        <v>-0.68810020876826083</v>
       </c>
       <c r="O52">
         <f t="shared" ca="1" si="3"/>
-        <v>0.12306064000000347</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.43454463999999354</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D53" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>58.200949999999999</v>
+        <v>57.880949999999999</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -3113,29 +3113,29 @@
       </c>
       <c r="J53">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.37</v>
+        <v>-0.4</v>
       </c>
       <c r="K53">
         <f t="shared" ca="1" si="7"/>
-        <v>0.79</v>
+        <v>0.18</v>
       </c>
       <c r="L53">
         <v>0.5</v>
       </c>
       <c r="M53">
         <f t="shared" ca="1" si="1"/>
-        <v>0.30094999999999944</v>
+        <v>-1.9050000000000594E-2</v>
       </c>
       <c r="N53">
         <f t="shared" ca="1" si="2"/>
-        <v>0.51977547495682952</v>
+        <v>-3.2901554404141109E-2</v>
       </c>
       <c r="O53">
         <f t="shared" ca="1" si="3"/>
-        <v>9.0570902499999661E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+        <v>3.6290250000002263E-4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="D54" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>38.992600000000003</v>
+        <v>38.787600000000005</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
@@ -3162,29 +3162,29 @@
       </c>
       <c r="J54">
         <f t="shared" ca="1" si="6"/>
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="K54">
         <f t="shared" ca="1" si="7"/>
-        <v>0.88</v>
+        <v>0.36</v>
       </c>
       <c r="L54">
         <v>0.5</v>
       </c>
       <c r="M54">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.0073999999999985</v>
+        <v>-1.2123999999999984</v>
       </c>
       <c r="N54">
         <f t="shared" ca="1" si="2"/>
-        <v>-2.5184999999999902</v>
+        <v>-3.0309999999999837</v>
       </c>
       <c r="O54">
         <f t="shared" ca="1" si="3"/>
-        <v>1.0148547599999971</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.4699137599999961</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="D55" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>21.6874</v>
+        <v>21.692450000000001</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
@@ -3211,29 +3211,29 @@
       </c>
       <c r="J55">
         <f t="shared" ca="1" si="6"/>
-        <v>2.5999999999999999E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="K55">
         <f t="shared" ca="1" si="7"/>
-        <v>-3.2000000000000002E-3</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="L55">
         <v>0.5</v>
       </c>
       <c r="M55">
         <f t="shared" ca="1" si="1"/>
-        <v>0.38739999999999886</v>
+        <v>0.3924499999999988</v>
       </c>
       <c r="N55">
         <f t="shared" ca="1" si="2"/>
-        <v>1.8187793427230092</v>
+        <v>1.8424882629108019</v>
       </c>
       <c r="O55">
         <f t="shared" ca="1" si="3"/>
-        <v>0.15007875999999912</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.15401700249999906</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="D56" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>113.9785</v>
+        <v>114.37350000000001</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
@@ -3260,29 +3260,29 @@
       </c>
       <c r="J56">
         <f t="shared" ca="1" si="6"/>
-        <v>0.19</v>
+        <v>-0.9</v>
       </c>
       <c r="K56">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.98</v>
+        <v>0.9</v>
       </c>
       <c r="L56">
         <v>0.5</v>
       </c>
       <c r="M56">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.42150000000000576</v>
+        <v>-2.6500000000005741E-2</v>
       </c>
       <c r="N56">
         <f t="shared" ca="1" si="2"/>
-        <v>-0.3684440559440616</v>
+        <v>-2.3164335664338509E-2</v>
       </c>
       <c r="O56">
         <f t="shared" ca="1" si="3"/>
-        <v>0.17766225000000485</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+        <v>7.022500000003043E-4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="D57" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>84.684950000000001</v>
+        <v>84.189949999999996</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
@@ -3313,25 +3313,25 @@
       </c>
       <c r="K57">
         <f t="shared" ca="1" si="7"/>
-        <v>0.97</v>
+        <v>-0.02</v>
       </c>
       <c r="L57">
         <v>0.5</v>
       </c>
       <c r="M57">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.11504999999999777</v>
+        <v>-0.61004999999999776</v>
       </c>
       <c r="N57">
         <f t="shared" ca="1" si="2"/>
-        <v>-0.13567216981131835</v>
+        <v>-0.71939858490566166</v>
       </c>
       <c r="O57">
         <f t="shared" ca="1" si="3"/>
-        <v>1.3236502499999485E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.37216100249999728</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D58" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>38.016449999999999</v>
+        <v>38.041449999999998</v>
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
@@ -3358,29 +3358,29 @@
       </c>
       <c r="J58">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.63</v>
+        <v>-0.85</v>
       </c>
       <c r="K58">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.31</v>
+        <v>-0.04</v>
       </c>
       <c r="L58">
         <v>0.5</v>
       </c>
       <c r="M58">
         <f t="shared" ca="1" si="1"/>
-        <v>1.2164500000000007</v>
+        <v>1.2414500000000006</v>
       </c>
       <c r="N58">
         <f t="shared" ca="1" si="2"/>
-        <v>3.305570652173917</v>
+        <v>3.3735054347826088</v>
       </c>
       <c r="O58">
         <f t="shared" ca="1" si="3"/>
-        <v>1.4797506025000018</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.5411981025000014</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="D59" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>115.22749999999999</v>
+        <v>116.2175</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
@@ -3407,29 +3407,29 @@
       </c>
       <c r="J59">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.02</v>
+        <v>0.85</v>
       </c>
       <c r="K59">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.46</v>
+        <v>0.65</v>
       </c>
       <c r="L59">
         <v>0.5</v>
       </c>
       <c r="M59">
         <f t="shared" ca="1" si="1"/>
-        <v>0.1274999999999997</v>
+        <v>1.1174999999999997</v>
       </c>
       <c r="N59">
         <f t="shared" ca="1" si="2"/>
-        <v>0.11077324066028904</v>
+        <v>0.97089487402259866</v>
       </c>
       <c r="O59">
         <f t="shared" ca="1" si="3"/>
-        <v>1.6256249999999924E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.2488062499999995</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="D60" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>71.665399999999991</v>
+        <v>71.540399999999991</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
@@ -3456,29 +3456,29 @@
       </c>
       <c r="J60">
         <f t="shared" ca="1" si="6"/>
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="K60">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.15</v>
+        <v>-0.39</v>
       </c>
       <c r="L60">
         <v>0.5</v>
       </c>
       <c r="M60">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.8346000000000033</v>
+        <v>-1.9596000000000036</v>
       </c>
       <c r="N60">
         <f t="shared" ca="1" si="2"/>
-        <v>-2.4960544217687231</v>
+        <v>-2.666122448979602</v>
       </c>
       <c r="O60">
         <f t="shared" ca="1" si="3"/>
-        <v>3.3657571600000122</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+        <v>3.840032160000014</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="D61" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>25.846550000000001</v>
+        <v>25.84385</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
@@ -3505,29 +3505,29 @@
       </c>
       <c r="J61">
         <f t="shared" ca="1" si="6"/>
-        <v>3.0999999999999999E-3</v>
+        <v>-4.7000000000000002E-3</v>
       </c>
       <c r="K61">
         <f t="shared" ca="1" si="7"/>
-        <v>-3.0000000000000001E-3</v>
+        <v>-5.9999999999999995E-4</v>
       </c>
       <c r="L61">
         <v>0.5</v>
       </c>
       <c r="M61">
         <f t="shared" ca="1" si="1"/>
-        <v>0.34655000000000069</v>
+        <v>0.34385000000000066</v>
       </c>
       <c r="N61">
         <f t="shared" ca="1" si="2"/>
-        <v>1.3590196078431482</v>
+        <v>1.3484313725490082</v>
       </c>
       <c r="O61">
         <f t="shared" ca="1" si="3"/>
-        <v>0.12009690250000048</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.11823282250000045</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="D62" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>132.34450000000001</v>
+        <v>132.6045</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
@@ -3554,29 +3554,29 @@
       </c>
       <c r="J62">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.95</v>
+        <v>-0.42</v>
       </c>
       <c r="K62">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="L62">
         <v>0.5</v>
       </c>
       <c r="M62">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.2554999999999923</v>
+        <v>-0.99549999999999217</v>
       </c>
       <c r="N62">
         <f t="shared" ca="1" si="2"/>
-        <v>-0.93974550898202613</v>
+        <v>-0.7451347305389211</v>
       </c>
       <c r="O62">
         <f t="shared" ca="1" si="3"/>
-        <v>1.5762802499999806</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.99102024999998439</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D63" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>98.337149999999994</v>
+        <v>98.412149999999997</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
@@ -3603,29 +3603,29 @@
       </c>
       <c r="J63">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.96</v>
+        <v>-0.47</v>
       </c>
       <c r="K63">
         <f t="shared" ca="1" si="7"/>
-        <v>0.64</v>
+        <v>0.3</v>
       </c>
       <c r="L63">
         <v>0.5</v>
       </c>
       <c r="M63">
         <f t="shared" ca="1" si="1"/>
-        <v>0.23715000000000347</v>
+        <v>0.31215000000000348</v>
       </c>
       <c r="N63">
         <f t="shared" ca="1" si="2"/>
-        <v>0.24174311926605796</v>
+        <v>0.31819571865443486</v>
       </c>
       <c r="O63">
         <f t="shared" ca="1" si="3"/>
-        <v>5.6240122500001648E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+        <v>9.7437622500002166E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="D64" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>83.394900000000007</v>
+        <v>83.814900000000009</v>
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
@@ -3652,29 +3652,29 @@
       </c>
       <c r="J64">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.6</v>
+        <v>0.25</v>
       </c>
       <c r="K64">
         <f t="shared" ca="1" si="7"/>
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="L64">
         <v>0.5</v>
       </c>
       <c r="M64">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.5050999999999994</v>
+        <v>-1.0850999999999993</v>
       </c>
       <c r="N64">
         <f t="shared" ca="1" si="2"/>
-        <v>-1.7727915194346244</v>
+        <v>-1.2780918727915203</v>
       </c>
       <c r="O64">
         <f t="shared" ca="1" si="3"/>
-        <v>2.2653260099999981</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.1774420099999985</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D65" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>56.399349999999998</v>
+        <v>55.979349999999997</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
@@ -3701,29 +3701,29 @@
       </c>
       <c r="J65">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.03</v>
+        <v>-0.85</v>
       </c>
       <c r="K65">
         <f t="shared" ca="1" si="7"/>
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="L65">
         <v>0.5</v>
       </c>
       <c r="M65">
         <f t="shared" ca="1" si="1"/>
-        <v>-0.80065000000000286</v>
+        <v>-1.2206500000000031</v>
       </c>
       <c r="N65">
         <f t="shared" ca="1" si="2"/>
-        <v>-1.3997377622377738</v>
+        <v>-2.1340034965035115</v>
       </c>
       <c r="O65">
         <f t="shared" ca="1" si="3"/>
-        <v>0.64104042250000459</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.4899864225000077</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="D66" s="4">
         <f t="shared" ca="1" si="0"/>
-        <v>56.553350000000002</v>
+        <v>56.25835</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
@@ -3750,29 +3750,29 @@
       </c>
       <c r="J66">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.14000000000000001</v>
+        <v>-0.37</v>
       </c>
       <c r="K66">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="L66">
         <v>0.5</v>
       </c>
       <c r="M66">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.4466500000000015</v>
+        <v>-1.7416500000000015</v>
       </c>
       <c r="N66">
         <f t="shared" ca="1" si="2"/>
-        <v>-2.4942241379310337</v>
+        <v>-3.0028448275862041</v>
       </c>
       <c r="O66">
         <f t="shared" ca="1" si="3"/>
-        <v>2.0927962225000045</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+        <v>3.0333447225000052</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D67" s="4">
         <f t="shared" ref="D67:D130" ca="1" si="8">B67+M67</f>
-        <v>46.488050000000001</v>
+        <v>47.26305</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
@@ -3799,29 +3799,29 @@
       </c>
       <c r="J67">
         <f t="shared" ca="1" si="6"/>
-        <v>-0.42</v>
+        <v>-0.34</v>
       </c>
       <c r="K67">
         <f t="shared" ca="1" si="7"/>
-        <v>-0.84</v>
+        <v>0.63</v>
       </c>
       <c r="L67">
         <v>0.5</v>
       </c>
       <c r="M67">
         <f t="shared" ref="M67:M130" ca="1" si="9">(I67+J67+K67)*L67</f>
-        <v>-0.71195000000000253</v>
+        <v>6.304999999999733E-2</v>
       </c>
       <c r="N67">
         <f t="shared" ref="N67:N130" ca="1" si="10">((D67/B67)-1)*100</f>
-        <v>-1.5083686440678035</v>
+        <v>0.13358050847456227</v>
       </c>
       <c r="O67">
         <f t="shared" ref="O67:O130" ca="1" si="11">M67^2</f>
-        <v>0.50687280250000355</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+        <v>3.9753024999996632E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="D68" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>38.868899999999996</v>
+        <v>38.843899999999998</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
@@ -3848,29 +3848,29 @@
       </c>
       <c r="J68">
         <f t="shared" ref="J68:J131" ca="1" si="14">IF(B68 &lt; 30, RANDBETWEEN(-100, 100) / 10000, RANDBETWEEN(-100,100) / 100)</f>
-        <v>0.56000000000000005</v>
+        <v>0.87</v>
       </c>
       <c r="K68">
         <f t="shared" ref="K68:K131" ca="1" si="15">IF(B68 &lt; 30, RANDBETWEEN(-100, 100) / 10000, RANDBETWEEN(-100,100) / 100)</f>
-        <v>-0.25</v>
+        <v>-0.61</v>
       </c>
       <c r="L68">
         <v>0.5</v>
       </c>
       <c r="M68">
         <f t="shared" ca="1" si="9"/>
-        <v>2.3688999999999991</v>
+        <v>2.3438999999999988</v>
       </c>
       <c r="N68">
         <f t="shared" ca="1" si="10"/>
-        <v>6.4901369863013647</v>
+        <v>6.4216438356164307</v>
       </c>
       <c r="O68">
         <f t="shared" ca="1" si="11"/>
-        <v>5.6116872099999959</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+        <v>5.4938672099999941</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="D69" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>27.750900000000001</v>
+        <v>27.754149999999999</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
@@ -3897,29 +3897,29 @@
       </c>
       <c r="J69">
         <f t="shared" ca="1" si="14"/>
-        <v>-3.8999999999999998E-3</v>
+        <v>-5.4000000000000003E-3</v>
       </c>
       <c r="K69">
         <f t="shared" ca="1" si="15"/>
-        <v>-5.0000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="L69">
         <v>0.5</v>
       </c>
       <c r="M69">
         <f t="shared" ca="1" si="9"/>
-        <v>-0.5491000000000007</v>
+        <v>-0.54585000000000083</v>
       </c>
       <c r="N69">
         <f t="shared" ca="1" si="10"/>
-        <v>-1.9402826855123623</v>
+        <v>-1.9287985865724444</v>
       </c>
       <c r="O69">
         <f t="shared" ca="1" si="11"/>
-        <v>0.30151081000000074</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.29795222250000092</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D70" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>49.234050000000003</v>
+        <v>50.21405</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
@@ -3946,29 +3946,29 @@
       </c>
       <c r="J70">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.99</v>
+        <v>0.92</v>
       </c>
       <c r="K70">
         <f t="shared" ca="1" si="15"/>
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L70">
         <v>0.5</v>
       </c>
       <c r="M70">
         <f t="shared" ca="1" si="9"/>
-        <v>0.23405000000000159</v>
+        <v>1.2140500000000016</v>
       </c>
       <c r="N70">
         <f t="shared" ca="1" si="10"/>
-        <v>0.47765306122449225</v>
+        <v>2.477653061224494</v>
       </c>
       <c r="O70">
         <f t="shared" ca="1" si="11"/>
-        <v>5.4779402500000747E-2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.4739174025000039</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="D71" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>25.241199999999999</v>
+        <v>25.240650000000002</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
@@ -3995,29 +3995,29 @@
       </c>
       <c r="J71">
         <f t="shared" ca="1" si="14"/>
-        <v>-5.4999999999999997E-3</v>
+        <v>-1.6999999999999999E-3</v>
       </c>
       <c r="K71">
         <f t="shared" ca="1" si="15"/>
-        <v>1.8E-3</v>
+        <v>-3.0999999999999999E-3</v>
       </c>
       <c r="L71">
         <v>0.5</v>
       </c>
       <c r="M71">
         <f t="shared" ca="1" si="9"/>
-        <v>2.2412000000000005</v>
+        <v>2.2406500000000005</v>
       </c>
       <c r="N71">
         <f t="shared" ca="1" si="10"/>
-        <v>9.7443478260869512</v>
+        <v>9.7419565217391479</v>
       </c>
       <c r="O71">
         <f t="shared" ca="1" si="11"/>
-        <v>5.0229774400000027</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+        <v>5.0205124225000022</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="D72" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>1.9617675000000001</v>
+        <v>1.9639175</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
@@ -4044,29 +4044,29 @@
       </c>
       <c r="J72">
         <f t="shared" ca="1" si="14"/>
-        <v>-2E-3</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="K72">
         <f t="shared" ca="1" si="15"/>
-        <v>-3.5999999999999999E-3</v>
+        <v>-6.7000000000000002E-3</v>
       </c>
       <c r="L72">
         <v>0.5</v>
       </c>
       <c r="M72">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.0382324999999999</v>
+        <v>-1.0360825</v>
       </c>
       <c r="N72">
         <f t="shared" ca="1" si="10"/>
-        <v>-34.607749999999996</v>
+        <v>-34.536083333333337</v>
       </c>
       <c r="O72">
         <f t="shared" ca="1" si="11"/>
-        <v>1.0779267240562498</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.0734669468062501</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="D73" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>53.414749999999998</v>
+        <v>53.879750000000001</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -4093,29 +4093,29 @@
       </c>
       <c r="J73">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.03</v>
+        <v>0.81</v>
       </c>
       <c r="K73">
         <f t="shared" ca="1" si="15"/>
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="L73">
         <v>0.5</v>
       </c>
       <c r="M73">
         <f t="shared" ca="1" si="9"/>
-        <v>1.4147499999999984</v>
+        <v>1.8797499999999983</v>
       </c>
       <c r="N73">
         <f t="shared" ca="1" si="10"/>
-        <v>2.7206730769230747</v>
+        <v>3.6149038461538385</v>
       </c>
       <c r="O73">
         <f t="shared" ca="1" si="11"/>
-        <v>2.0015175624999957</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+        <v>3.5334600624999934</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="D74" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>55.336399999999998</v>
+        <v>55.561399999999999</v>
       </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
@@ -4142,29 +4142,29 @@
       </c>
       <c r="J74">
         <f t="shared" ca="1" si="14"/>
-        <v>0.44</v>
+        <v>0.85</v>
       </c>
       <c r="K74">
         <f t="shared" ca="1" si="15"/>
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="L74">
         <v>0.5</v>
       </c>
       <c r="M74">
         <f t="shared" ca="1" si="9"/>
-        <v>2.3364000000000007</v>
+        <v>2.5614000000000003</v>
       </c>
       <c r="N74">
         <f t="shared" ca="1" si="10"/>
-        <v>4.4083018867924428</v>
+        <v>4.832830188679238</v>
       </c>
       <c r="O74">
         <f t="shared" ca="1" si="11"/>
-        <v>5.4587649600000034</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+        <v>6.5607699600000018</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="D75" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>29.047000000000001</v>
+        <v>29.054949999999998</v>
       </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
@@ -4191,29 +4191,29 @@
       </c>
       <c r="J75">
         <f t="shared" ca="1" si="14"/>
-        <v>-4.4999999999999997E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="K75">
         <f t="shared" ca="1" si="15"/>
-        <v>8.9999999999999998E-4</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="L75">
         <v>0.5</v>
       </c>
       <c r="M75">
         <f t="shared" ca="1" si="9"/>
-        <v>2.0469999999999997</v>
+        <v>2.0549499999999998</v>
       </c>
       <c r="N75">
         <f t="shared" ca="1" si="10"/>
-        <v>7.5814814814814779</v>
+        <v>7.6109259259259154</v>
       </c>
       <c r="O75">
         <f t="shared" ca="1" si="11"/>
-        <v>4.1902089999999985</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4.2228195024999993</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="D76" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>12.683299999999999</v>
+        <v>12.68235</v>
       </c>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
@@ -4240,29 +4240,29 @@
       </c>
       <c r="J76">
         <f t="shared" ca="1" si="14"/>
-        <v>2.0000000000000001E-4</v>
+        <v>1.9E-3</v>
       </c>
       <c r="K76">
         <f t="shared" ca="1" si="15"/>
-        <v>5.0000000000000001E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="L76">
         <v>0.5</v>
       </c>
       <c r="M76">
         <f t="shared" ca="1" si="9"/>
-        <v>1.6832999999999998</v>
+        <v>1.6823499999999998</v>
       </c>
       <c r="N76">
         <f t="shared" ca="1" si="10"/>
-        <v>15.302727272727257</v>
+        <v>15.294090909090908</v>
       </c>
       <c r="O76">
         <f t="shared" ca="1" si="11"/>
-        <v>2.8334988899999991</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2.8303015224999992</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="D77" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>5.1785350000000001</v>
+        <v>5.1710349999999998</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -4289,29 +4289,29 @@
       </c>
       <c r="J77">
         <f t="shared" ca="1" si="14"/>
-        <v>7.3000000000000001E-3</v>
+        <v>-3.5999999999999999E-3</v>
       </c>
       <c r="K77">
         <f t="shared" ca="1" si="15"/>
-        <v>5.1999999999999998E-3</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="L77">
         <v>0.5</v>
       </c>
       <c r="M77">
         <f t="shared" ca="1" si="9"/>
-        <v>-0.82146499999999989</v>
+        <v>-0.82896499999999995</v>
       </c>
       <c r="N77">
         <f t="shared" ca="1" si="10"/>
-        <v>-13.691083333333331</v>
+        <v>-13.81608333333334</v>
       </c>
       <c r="O77">
         <f t="shared" ca="1" si="11"/>
-        <v>0.67480474622499986</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.68718297122499994</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="D78" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>57.893549999999998</v>
+        <v>58.588549999999998</v>
       </c>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
@@ -4338,29 +4338,29 @@
       </c>
       <c r="J78">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.37</v>
+        <v>-0.12</v>
       </c>
       <c r="K78">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.37</v>
+        <v>0.77</v>
       </c>
       <c r="L78">
         <v>0.5</v>
       </c>
       <c r="M78">
         <f t="shared" ca="1" si="9"/>
-        <v>0.89354999999999851</v>
+        <v>1.5885499999999986</v>
       </c>
       <c r="N78">
         <f t="shared" ca="1" si="10"/>
-        <v>1.5676315789473705</v>
+        <v>2.7869298245613905</v>
       </c>
       <c r="O78">
         <f t="shared" ca="1" si="11"/>
-        <v>0.79843160249999734</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2.5234911024999955</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D79" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>63.865749999999998</v>
+        <v>64.410749999999993</v>
       </c>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
@@ -4387,29 +4387,29 @@
       </c>
       <c r="J79">
         <f t="shared" ca="1" si="14"/>
-        <v>0.18</v>
+        <v>-0.15</v>
       </c>
       <c r="K79">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.52</v>
+        <v>0.9</v>
       </c>
       <c r="L79">
         <v>0.5</v>
       </c>
       <c r="M79">
         <f t="shared" ca="1" si="9"/>
-        <v>-2.1342499999999998</v>
+        <v>-1.5892500000000001</v>
       </c>
       <c r="N79">
         <f t="shared" ca="1" si="10"/>
-        <v>-3.2337121212121289</v>
+        <v>-2.4079545454545603</v>
       </c>
       <c r="O79">
         <f t="shared" ca="1" si="11"/>
-        <v>4.5550230624999992</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2.5257155625000003</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="D80" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>20.806750000000001</v>
+        <v>20.802700000000002</v>
       </c>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
@@ -4436,29 +4436,29 @@
       </c>
       <c r="J80">
         <f t="shared" ca="1" si="14"/>
-        <v>-8.8999999999999999E-3</v>
+        <v>-7.1999999999999998E-3</v>
       </c>
       <c r="K80">
         <f t="shared" ca="1" si="15"/>
-        <v>5.0000000000000001E-3</v>
+        <v>-4.7999999999999996E-3</v>
       </c>
       <c r="L80">
         <v>0.5</v>
       </c>
       <c r="M80">
         <f t="shared" ca="1" si="9"/>
-        <v>-0.19325000000000003</v>
+        <v>-0.19730000000000003</v>
       </c>
       <c r="N80">
         <f t="shared" ca="1" si="10"/>
-        <v>-0.92023809523809064</v>
+        <v>-0.93952380952380121</v>
       </c>
       <c r="O80">
         <f t="shared" ca="1" si="11"/>
-        <v>3.7345562500000012E-2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+        <v>3.892729000000001E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="D81" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>11.0344</v>
+        <v>11.0222</v>
       </c>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
@@ -4485,29 +4485,29 @@
       </c>
       <c r="J81">
         <f t="shared" ca="1" si="14"/>
-        <v>8.3000000000000001E-3</v>
+        <v>-5.7999999999999996E-3</v>
       </c>
       <c r="K81">
         <f t="shared" ca="1" si="15"/>
-        <v>1.6999999999999999E-3</v>
+        <v>-8.6E-3</v>
       </c>
       <c r="L81">
         <v>0.5</v>
       </c>
       <c r="M81">
         <f t="shared" ca="1" si="9"/>
-        <v>-0.96560000000000012</v>
+        <v>-0.97780000000000011</v>
       </c>
       <c r="N81">
         <f t="shared" ca="1" si="10"/>
-        <v>-8.0466666666666686</v>
+        <v>-8.1483333333333352</v>
       </c>
       <c r="O81">
         <f t="shared" ca="1" si="11"/>
-        <v>0.93238336000000022</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.95609284000000028</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="D82" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>65.157299999999992</v>
+        <v>66.027299999999997</v>
       </c>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
@@ -4534,29 +4534,29 @@
       </c>
       <c r="J82">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.28000000000000003</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K82">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.72</v>
+        <v>0.67</v>
       </c>
       <c r="L82">
         <v>0.5</v>
       </c>
       <c r="M82">
         <f t="shared" ca="1" si="9"/>
-        <v>1.1572999999999993</v>
+        <v>2.0272999999999994</v>
       </c>
       <c r="N82">
         <f t="shared" ca="1" si="10"/>
-        <v>1.8082812499999878</v>
+        <v>3.167656249999995</v>
       </c>
       <c r="O82">
         <f t="shared" ca="1" si="11"/>
-        <v>1.3393432899999984</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4.109945289999998</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="D83" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>73.794600000000003</v>
+        <v>73.544600000000003</v>
       </c>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
@@ -4583,29 +4583,29 @@
       </c>
       <c r="J83">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.2</v>
+        <v>-0.45</v>
       </c>
       <c r="K83">
         <f t="shared" ca="1" si="15"/>
-        <v>0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="L83">
         <v>0.5</v>
       </c>
       <c r="M83">
         <f t="shared" ca="1" si="9"/>
-        <v>-4.2053999999999983</v>
+        <v>-4.4553999999999983</v>
       </c>
       <c r="N83">
         <f t="shared" ca="1" si="10"/>
-        <v>-5.3915384615384587</v>
+        <v>-5.7120512820512781</v>
       </c>
       <c r="O83">
         <f t="shared" ca="1" si="11"/>
-        <v>17.685389159999986</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+        <v>19.850589159999984</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="D84" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>62.823100000000004</v>
+        <v>62.018100000000004</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
@@ -4632,29 +4632,29 @@
       </c>
       <c r="J84">
         <f t="shared" ca="1" si="14"/>
-        <v>0.89</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="K84">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.09</v>
+        <v>-0.52</v>
       </c>
       <c r="L84">
         <v>0.5</v>
       </c>
       <c r="M84">
         <f t="shared" ca="1" si="9"/>
-        <v>-2.1768999999999985</v>
+        <v>-2.9818999999999987</v>
       </c>
       <c r="N84">
         <f t="shared" ca="1" si="10"/>
-        <v>-3.3490769230769213</v>
+        <v>-4.587538461538454</v>
       </c>
       <c r="O84">
         <f t="shared" ca="1" si="11"/>
-        <v>4.7388936099999937</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+        <v>8.8917276099999913</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="D85" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>40.569049999999997</v>
+        <v>40.704050000000002</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
@@ -4681,29 +4681,29 @@
       </c>
       <c r="J85">
         <f t="shared" ca="1" si="14"/>
-        <v>0.08</v>
+        <v>-0.48</v>
       </c>
       <c r="K85">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.45</v>
+        <v>0.38</v>
       </c>
       <c r="L85">
         <v>0.5</v>
       </c>
       <c r="M85">
         <f t="shared" ca="1" si="9"/>
-        <v>3.5690499999999994</v>
+        <v>3.7040499999999992</v>
       </c>
       <c r="N85">
         <f t="shared" ca="1" si="10"/>
-        <v>9.6460810810810713</v>
+        <v>10.010945945945959</v>
       </c>
       <c r="O85">
         <f t="shared" ca="1" si="11"/>
-        <v>12.738117902499996</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+        <v>13.719986402499995</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="D86" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>36.9133</v>
+        <v>36.888300000000001</v>
       </c>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
@@ -4730,29 +4730,29 @@
       </c>
       <c r="J86">
         <f t="shared" ca="1" si="14"/>
-        <v>0.72</v>
+        <v>0.13</v>
       </c>
       <c r="K86">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.89</v>
+        <v>-0.35</v>
       </c>
       <c r="L86">
         <v>0.5</v>
       </c>
       <c r="M86">
         <f t="shared" ca="1" si="9"/>
-        <v>-0.58669999999999956</v>
+        <v>-0.61169999999999958</v>
       </c>
       <c r="N86">
         <f t="shared" ca="1" si="10"/>
-        <v>-1.56453333333334</v>
+        <v>-1.6311999999999993</v>
       </c>
       <c r="O86">
         <f t="shared" ca="1" si="11"/>
-        <v>0.3442168899999995</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.37417688999999948</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="D87" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>31.339749999999999</v>
+        <v>31.399750000000001</v>
       </c>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
@@ -4779,29 +4779,29 @@
       </c>
       <c r="J87">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.9</v>
+        <v>-0.69</v>
       </c>
       <c r="K87">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.34</v>
+        <v>-0.43</v>
       </c>
       <c r="L87">
         <v>0.5</v>
       </c>
       <c r="M87">
         <f t="shared" ca="1" si="9"/>
-        <v>-0.16025000000000036</v>
+        <v>-0.10025000000000031</v>
       </c>
       <c r="N87">
         <f t="shared" ca="1" si="10"/>
-        <v>-0.50873015873016403</v>
+        <v>-0.31825396825396757</v>
       </c>
       <c r="O87">
         <f t="shared" ca="1" si="11"/>
-        <v>2.5680062500000118E-2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.0050062500000062E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="D88" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>30.488499999999998</v>
+        <v>30.491399999999999</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -4828,29 +4828,29 @@
       </c>
       <c r="J88">
         <f t="shared" ca="1" si="14"/>
-        <v>2.2000000000000001E-3</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="K88">
         <f t="shared" ca="1" si="15"/>
-        <v>-9.1000000000000004E-3</v>
+        <v>-1.8E-3</v>
       </c>
       <c r="L88">
         <v>0.5</v>
       </c>
       <c r="M88">
         <f t="shared" ca="1" si="9"/>
-        <v>1.0885000000000007</v>
+        <v>1.0914000000000008</v>
       </c>
       <c r="N88">
         <f t="shared" ca="1" si="10"/>
-        <v>3.702380952380957</v>
+        <v>3.7122448979591827</v>
       </c>
       <c r="O88">
         <f t="shared" ca="1" si="11"/>
-        <v>1.1848322500000015</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.1911539600000018</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="D89" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>34.479500000000002</v>
+        <v>34.694499999999998</v>
       </c>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
@@ -4877,29 +4877,29 @@
       </c>
       <c r="J89">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.12</v>
+        <v>0.35</v>
       </c>
       <c r="K89">
         <f t="shared" ca="1" si="15"/>
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="L89">
         <v>0.5</v>
       </c>
       <c r="M89">
         <f t="shared" ca="1" si="9"/>
-        <v>-0.22050000000000181</v>
+        <v>-5.5000000000018368E-3</v>
       </c>
       <c r="N89">
         <f t="shared" ca="1" si="10"/>
-        <v>-0.63544668587897091</v>
+        <v>-1.5850144092233176E-2</v>
       </c>
       <c r="O89">
         <f t="shared" ca="1" si="11"/>
-        <v>4.8620250000000795E-2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+        <v>3.0250000000020203E-5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="D90" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>46.555149999999998</v>
+        <v>45.93515</v>
       </c>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
@@ -4926,29 +4926,29 @@
       </c>
       <c r="J90">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.66</v>
+        <v>0.04</v>
       </c>
       <c r="K90">
         <f t="shared" ca="1" si="15"/>
-        <v>0.94</v>
+        <v>-1</v>
       </c>
       <c r="L90">
         <v>0.5</v>
       </c>
       <c r="M90">
         <f t="shared" ca="1" si="9"/>
-        <v>2.0551500000000003</v>
+        <v>1.4351500000000006</v>
       </c>
       <c r="N90">
         <f t="shared" ca="1" si="10"/>
-        <v>4.6183146067415581</v>
+        <v>3.2250561797752875</v>
       </c>
       <c r="O90">
         <f t="shared" ca="1" si="11"/>
-        <v>4.2236415225000012</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2.0596555225000017</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="D91" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>46.131500000000003</v>
+        <v>45.716500000000003</v>
       </c>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
@@ -4975,29 +4975,29 @@
       </c>
       <c r="J91">
         <f t="shared" ca="1" si="14"/>
-        <v>0.39</v>
+        <v>0.31</v>
       </c>
       <c r="K91">
         <f t="shared" ca="1" si="15"/>
-        <v>0.56000000000000005</v>
+        <v>-0.19</v>
       </c>
       <c r="L91">
         <v>0.5</v>
       </c>
       <c r="M91">
         <f t="shared" ca="1" si="9"/>
-        <v>-0.36849999999999872</v>
+        <v>-0.78349999999999875</v>
       </c>
       <c r="N91">
         <f t="shared" ca="1" si="10"/>
-        <v>-0.79247311827956857</v>
+        <v>-1.6849462365591372</v>
       </c>
       <c r="O91">
         <f t="shared" ca="1" si="11"/>
-        <v>0.13579224999999906</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.61387224999999801</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="D92" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>46.639899999999997</v>
+        <v>47.489899999999999</v>
       </c>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
@@ -5024,29 +5024,29 @@
       </c>
       <c r="J92">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.81</v>
+        <v>0.64</v>
       </c>
       <c r="K92">
         <f t="shared" ca="1" si="15"/>
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="L92">
         <v>0.5</v>
       </c>
       <c r="M92">
         <f t="shared" ca="1" si="9"/>
-        <v>-2.2601000000000013</v>
+        <v>-1.410100000000001</v>
       </c>
       <c r="N92">
         <f t="shared" ca="1" si="10"/>
-        <v>-4.6218813905930523</v>
+        <v>-2.8836400817995878</v>
       </c>
       <c r="O92">
         <f t="shared" ca="1" si="11"/>
-        <v>5.108052010000006</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.9883820100000029</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="D93" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>81.187899999999999</v>
+        <v>80.962899999999991</v>
       </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
@@ -5073,29 +5073,29 @@
       </c>
       <c r="J93">
         <f t="shared" ca="1" si="14"/>
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="K93">
         <f t="shared" ca="1" si="15"/>
-        <v>0.42</v>
+        <v>0.02</v>
       </c>
       <c r="L93">
         <v>0.5</v>
       </c>
       <c r="M93">
         <f t="shared" ca="1" si="9"/>
-        <v>0.58790000000000309</v>
+        <v>0.36290000000000305</v>
       </c>
       <c r="N93">
         <f t="shared" ca="1" si="10"/>
-        <v>0.7294044665012489</v>
+        <v>0.45024813895782057</v>
       </c>
       <c r="O93">
         <f t="shared" ca="1" si="11"/>
-        <v>0.3456264100000036</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.13169641000000221</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D94" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>79.627899999999997</v>
+        <v>79.607900000000001</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
@@ -5122,29 +5122,29 @@
       </c>
       <c r="J94">
         <f t="shared" ca="1" si="14"/>
-        <v>0.14000000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="K94">
         <f t="shared" ca="1" si="15"/>
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="L94">
         <v>0.5</v>
       </c>
       <c r="M94">
         <f t="shared" ca="1" si="9"/>
-        <v>-0.87210000000000054</v>
+        <v>-0.89210000000000056</v>
       </c>
       <c r="N94">
         <f t="shared" ca="1" si="10"/>
-        <v>-1.0833540372670813</v>
+        <v>-1.1081987577639785</v>
       </c>
       <c r="O94">
         <f t="shared" ca="1" si="11"/>
-        <v>0.76055841000000091</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.795842410000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="D95" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>73.586950000000002</v>
+        <v>72.476950000000002</v>
       </c>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
@@ -5171,29 +5171,29 @@
       </c>
       <c r="J95">
         <f t="shared" ca="1" si="14"/>
-        <v>0.81</v>
+        <v>-0.22</v>
       </c>
       <c r="K95">
         <f t="shared" ca="1" si="15"/>
-        <v>0.78</v>
+        <v>-0.41</v>
       </c>
       <c r="L95">
         <v>0.5</v>
       </c>
       <c r="M95">
         <f t="shared" ca="1" si="9"/>
-        <v>5.7869500000000027</v>
+        <v>4.6769500000000024</v>
       </c>
       <c r="N95">
         <f t="shared" ca="1" si="10"/>
-        <v>8.535324483775808</v>
+        <v>6.8981563421828929</v>
       </c>
       <c r="O95">
         <f t="shared" ca="1" si="11"/>
-        <v>33.488790302500028</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+        <v>21.873861302500021</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="D96" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>78.235350000000011</v>
+        <v>77.755350000000007</v>
       </c>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
@@ -5220,29 +5220,29 @@
       </c>
       <c r="J96">
         <f t="shared" ca="1" si="14"/>
-        <v>0.25</v>
+        <v>-0.3</v>
       </c>
       <c r="K96">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.17</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="L96">
         <v>0.5</v>
       </c>
       <c r="M96">
         <f t="shared" ca="1" si="9"/>
-        <v>-0.66465000000000085</v>
+        <v>-1.1446500000000008</v>
       </c>
       <c r="N96">
         <f t="shared" ca="1" si="10"/>
-        <v>-0.84239543726235544</v>
+        <v>-1.4507604562737586</v>
       </c>
       <c r="O96">
         <f t="shared" ca="1" si="11"/>
-        <v>0.44175962250000111</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1.3102236225000019</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="D97" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>81.613550000000004</v>
+        <v>81.723550000000003</v>
       </c>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
@@ -5269,29 +5269,29 @@
       </c>
       <c r="J97">
         <f t="shared" ca="1" si="14"/>
-        <v>0.79</v>
+        <v>0.94</v>
       </c>
       <c r="K97">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.75</v>
+        <v>-0.68</v>
       </c>
       <c r="L97">
         <v>0.5</v>
       </c>
       <c r="M97">
         <f t="shared" ca="1" si="9"/>
-        <v>-2.0864500000000024</v>
+        <v>-1.9764500000000025</v>
       </c>
       <c r="N97">
         <f t="shared" ca="1" si="10"/>
-        <v>-2.4927718040621216</v>
+        <v>-2.3613500597371551</v>
       </c>
       <c r="O97">
         <f t="shared" ca="1" si="11"/>
-        <v>4.3532736025000096</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+        <v>3.9063546025000098</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="D98" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>86.341949999999997</v>
+        <v>87.736950000000007</v>
       </c>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
@@ -5318,29 +5318,29 @@
       </c>
       <c r="J98">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.83</v>
+        <v>0.72</v>
       </c>
       <c r="K98">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.96</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="L98">
         <v>0.5</v>
       </c>
       <c r="M98">
         <f t="shared" ca="1" si="9"/>
-        <v>1.2419500000000059</v>
+        <v>2.6369500000000059</v>
       </c>
       <c r="N98">
         <f t="shared" ca="1" si="10"/>
-        <v>1.4594007050528823</v>
+        <v>3.0986486486486609</v>
       </c>
       <c r="O98">
         <f t="shared" ca="1" si="11"/>
-        <v>1.5424398025000146</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+        <v>6.9535053025000311</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="D99" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>86.394599999999997</v>
+        <v>87.104600000000005</v>
       </c>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
@@ -5367,29 +5367,29 @@
       </c>
       <c r="J99">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.39</v>
+        <v>-0.63</v>
       </c>
       <c r="K99">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.9</v>
+        <v>0.76</v>
       </c>
       <c r="L99">
         <v>0.5</v>
       </c>
       <c r="M99">
         <f t="shared" ca="1" si="9"/>
-        <v>1.1945999999999972</v>
+        <v>1.9045999999999972</v>
       </c>
       <c r="N99">
         <f t="shared" ca="1" si="10"/>
-        <v>1.4021126760563218</v>
+        <v>2.2354460093896744</v>
       </c>
       <c r="O99">
         <f t="shared" ca="1" si="11"/>
-        <v>1.4270691599999934</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+        <v>3.6275011599999893</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="D100" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>92.190749999999994</v>
+        <v>92.405749999999998</v>
       </c>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
@@ -5416,29 +5416,29 @@
       </c>
       <c r="J100">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.4</v>
+        <v>-0.27</v>
       </c>
       <c r="K100">
         <f t="shared" ca="1" si="15"/>
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="L100">
         <v>0.5</v>
       </c>
       <c r="M100">
         <f t="shared" ca="1" si="9"/>
-        <v>-2.4092499999999997</v>
+        <v>-2.1942499999999994</v>
       </c>
       <c r="N100">
         <f t="shared" ca="1" si="10"/>
-        <v>-2.5467758985200817</v>
+        <v>-2.3195031712473502</v>
       </c>
       <c r="O100">
         <f t="shared" ca="1" si="11"/>
-        <v>5.8044855624999983</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+        <v>4.8147330624999976</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="D101" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>97.503299999999996</v>
+        <v>97.553300000000007</v>
       </c>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
@@ -5465,29 +5465,29 @@
       </c>
       <c r="J101">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.54</v>
+        <v>0.2</v>
       </c>
       <c r="K101">
         <f t="shared" ca="1" si="15"/>
-        <v>0.69</v>
+        <v>0.05</v>
       </c>
       <c r="L101">
         <v>0.5</v>
       </c>
       <c r="M101">
         <f t="shared" ca="1" si="9"/>
-        <v>-3.7966999999999969</v>
+        <v>-3.746699999999997</v>
       </c>
       <c r="N101">
         <f t="shared" ca="1" si="10"/>
-        <v>-3.7479763079960482</v>
+        <v>-3.6986179664363128</v>
       </c>
       <c r="O101">
         <f t="shared" ca="1" si="11"/>
-        <v>14.414930889999976</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+        <v>14.037760889999978</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="D102" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>72.713250000000002</v>
+        <v>72.958249999999992</v>
       </c>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
@@ -5514,29 +5514,29 @@
       </c>
       <c r="J102">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.43</v>
+        <v>0.4</v>
       </c>
       <c r="K102">
         <f t="shared" ca="1" si="15"/>
-        <v>0.7</v>
+        <v>0.36</v>
       </c>
       <c r="L102">
         <v>0.5</v>
       </c>
       <c r="M102">
         <f t="shared" ca="1" si="9"/>
-        <v>-2.5867499999999999</v>
+        <v>-2.3417499999999998</v>
       </c>
       <c r="N102">
         <f t="shared" ca="1" si="10"/>
-        <v>-3.4352589641434172</v>
+        <v>-3.1098937583001418</v>
       </c>
       <c r="O102">
         <f t="shared" ca="1" si="11"/>
-        <v>6.6912755624999996</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+        <v>5.4837930624999993</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="D103" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>36.653599999999997</v>
+        <v>36.723599999999998</v>
       </c>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
@@ -5563,29 +5563,29 @@
       </c>
       <c r="J103">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.34</v>
+        <v>0.31</v>
       </c>
       <c r="K103">
         <f t="shared" ca="1" si="15"/>
-        <v>0.08</v>
+        <v>-0.43</v>
       </c>
       <c r="L103">
         <v>0.5</v>
       </c>
       <c r="M103">
         <f t="shared" ca="1" si="9"/>
-        <v>1.2536000000000014</v>
+        <v>1.3236000000000012</v>
       </c>
       <c r="N103">
         <f t="shared" ca="1" si="10"/>
-        <v>3.5412429378530952</v>
+        <v>3.7389830508474553</v>
       </c>
       <c r="O103">
         <f t="shared" ca="1" si="11"/>
-        <v>1.5715129600000035</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1.7519169600000033</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="D104" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>74.156999999999996</v>
+        <v>74.777000000000001</v>
       </c>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
@@ -5612,29 +5612,29 @@
       </c>
       <c r="J104">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.54</v>
+        <v>0.38</v>
       </c>
       <c r="K104">
         <f t="shared" ca="1" si="15"/>
-        <v>0.05</v>
+        <v>0.37</v>
       </c>
       <c r="L104">
         <v>0.5</v>
       </c>
       <c r="M104">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.0430000000000019</v>
+        <v>-0.42300000000000187</v>
       </c>
       <c r="N104">
         <f t="shared" ca="1" si="10"/>
-        <v>-1.3869680851063881</v>
+        <v>-0.56249999999999911</v>
       </c>
       <c r="O104">
         <f t="shared" ca="1" si="11"/>
-        <v>1.0878490000000041</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.17892900000000159</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="D105" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>72.623400000000004</v>
+        <v>73.413399999999996</v>
       </c>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
@@ -5661,29 +5661,29 @@
       </c>
       <c r="J105">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.64</v>
+        <v>0.02</v>
       </c>
       <c r="K105">
         <f t="shared" ca="1" si="15"/>
-        <v>0.08</v>
+        <v>1</v>
       </c>
       <c r="L105">
         <v>0.5</v>
       </c>
       <c r="M105">
         <f t="shared" ca="1" si="9"/>
-        <v>-0.67659999999999942</v>
+        <v>0.11340000000000061</v>
       </c>
       <c r="N105">
         <f t="shared" ca="1" si="10"/>
-        <v>-0.92305593451568191</v>
+        <v>0.15470668485675354</v>
       </c>
       <c r="O105">
         <f t="shared" ca="1" si="11"/>
-        <v>0.45778755999999921</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1.2859560000000138E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="D106" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>60.629399999999997</v>
+        <v>61.384399999999999</v>
       </c>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
@@ -5710,29 +5710,29 @@
       </c>
       <c r="J106">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.43</v>
+        <v>0.3</v>
       </c>
       <c r="K106">
         <f t="shared" ca="1" si="15"/>
-        <v>0.13</v>
+        <v>0.91</v>
       </c>
       <c r="L106">
         <v>0.5</v>
       </c>
       <c r="M106">
         <f t="shared" ca="1" si="9"/>
-        <v>0.22940000000000041</v>
+        <v>0.98440000000000039</v>
       </c>
       <c r="N106">
         <f t="shared" ca="1" si="10"/>
-        <v>0.37980132450330384</v>
+        <v>1.6298013245033216</v>
       </c>
       <c r="O106">
         <f t="shared" ca="1" si="11"/>
-        <v>5.2624360000000189E-2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.9690433600000008</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="D107" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>41.356700000000004</v>
+        <v>41.276700000000005</v>
       </c>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
@@ -5759,29 +5759,29 @@
       </c>
       <c r="J107">
         <f t="shared" ca="1" si="14"/>
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="K107">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.31</v>
+        <v>-0.18</v>
       </c>
       <c r="L107">
         <v>0.5</v>
       </c>
       <c r="M107">
         <f t="shared" ca="1" si="9"/>
-        <v>2.156699999999999</v>
+        <v>2.0766999999999989</v>
       </c>
       <c r="N107">
         <f t="shared" ca="1" si="10"/>
-        <v>5.5017857142857229</v>
+        <v>5.2977040816326593</v>
       </c>
       <c r="O107">
         <f t="shared" ca="1" si="11"/>
-        <v>4.6513548899999959</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+        <v>4.3126828899999952</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="D108" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>75.69765000000001</v>
+        <v>74.507649999999998</v>
       </c>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
@@ -5808,29 +5808,29 @@
       </c>
       <c r="J108">
         <f t="shared" ca="1" si="14"/>
-        <v>0.45</v>
+        <v>-0.86</v>
       </c>
       <c r="K108">
         <f t="shared" ca="1" si="15"/>
-        <v>0.74</v>
+        <v>-0.33</v>
       </c>
       <c r="L108">
         <v>0.5</v>
       </c>
       <c r="M108">
         <f t="shared" ca="1" si="9"/>
-        <v>-2.349999999998742E-3</v>
+        <v>-1.1923499999999987</v>
       </c>
       <c r="N108">
         <f t="shared" ca="1" si="10"/>
-        <v>-3.1043593130664071E-3</v>
+        <v>-1.5750990752972371</v>
       </c>
       <c r="O108">
         <f t="shared" ca="1" si="11"/>
-        <v>5.5224999999940869E-6</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1.421698522499997</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="D109" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>74.680549999999997</v>
+        <v>75.52055</v>
       </c>
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
@@ -5857,29 +5857,29 @@
       </c>
       <c r="J109">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.6</v>
+        <v>0.46</v>
       </c>
       <c r="K109">
         <f t="shared" ca="1" si="15"/>
-        <v>0.2</v>
+        <v>0.82</v>
       </c>
       <c r="L109">
         <v>0.5</v>
       </c>
       <c r="M109">
         <f t="shared" ca="1" si="9"/>
-        <v>-0.71945000000000625</v>
+        <v>0.12054999999999377</v>
       </c>
       <c r="N109">
         <f t="shared" ca="1" si="10"/>
-        <v>-0.95417771883290481</v>
+        <v>0.15988063660477003</v>
       </c>
       <c r="O109">
         <f t="shared" ca="1" si="11"/>
-        <v>0.517608302500009</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1.4532302499998498E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="D110" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>36.682100000000005</v>
+        <v>36.397100000000002</v>
       </c>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
@@ -5906,33 +5906,33 @@
       </c>
       <c r="J110">
         <f t="shared" ca="1" si="14"/>
-        <v>0.95</v>
+        <v>0.36</v>
       </c>
       <c r="K110">
         <f t="shared" ca="1" si="15"/>
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="L110">
         <v>0.5</v>
       </c>
       <c r="M110">
         <f t="shared" ca="1" si="9"/>
-        <v>2.4820999999999991</v>
+        <v>2.1970999999999989</v>
       </c>
       <c r="N110">
         <f t="shared" ca="1" si="10"/>
-        <v>7.2576023391812905</v>
+        <v>6.4242690058479601</v>
       </c>
       <c r="O110">
         <f t="shared" ca="1" si="11"/>
-        <v>6.160820409999995</v>
+        <v>4.8272484099999957</v>
       </c>
       <c r="P110">
         <f ca="1">SUM(O3:O459)</f>
-        <v>748.87851942723171</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+        <v>748.2979679469812</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="D111" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>32.781799999999997</v>
+        <v>32.681800000000003</v>
       </c>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
@@ -5959,29 +5959,29 @@
       </c>
       <c r="J111">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.25</v>
+        <v>-0.44</v>
       </c>
       <c r="K111">
         <f t="shared" ca="1" si="15"/>
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="L111">
         <v>0.5</v>
       </c>
       <c r="M111">
         <f t="shared" ca="1" si="9"/>
-        <v>1.1817999999999986</v>
+        <v>1.0817999999999985</v>
       </c>
       <c r="N111">
         <f t="shared" ca="1" si="10"/>
-        <v>3.7398734177215065</v>
+        <v>3.4234177215189954</v>
       </c>
       <c r="O111">
         <f t="shared" ca="1" si="11"/>
-        <v>1.3966512399999969</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1.1702912399999967</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="D112" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>44.887299999999996</v>
+        <v>44.372299999999996</v>
       </c>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
@@ -6008,29 +6008,29 @@
       </c>
       <c r="J112">
         <f t="shared" ca="1" si="14"/>
-        <v>0.39</v>
+        <v>0.11</v>
       </c>
       <c r="K112">
         <f t="shared" ca="1" si="15"/>
-        <v>7.0000000000000007E-2</v>
+        <v>-0.68</v>
       </c>
       <c r="L112">
         <v>0.5</v>
       </c>
       <c r="M112">
         <f t="shared" ca="1" si="9"/>
-        <v>1.4873000000000007</v>
+        <v>0.97230000000000061</v>
       </c>
       <c r="N112">
         <f t="shared" ca="1" si="10"/>
-        <v>3.4269585253456247</v>
+        <v>2.2403225806451488</v>
       </c>
       <c r="O112">
         <f t="shared" ca="1" si="11"/>
-        <v>2.2120612900000021</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.94536729000000119</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="D113" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>54.111400000000003</v>
+        <v>53.9664</v>
       </c>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
@@ -6057,29 +6057,29 @@
       </c>
       <c r="J113">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.65</v>
+        <v>0.59</v>
       </c>
       <c r="K113">
         <f t="shared" ca="1" si="15"/>
-        <v>0.95</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="L113">
         <v>0.5</v>
       </c>
       <c r="M113">
         <f t="shared" ca="1" si="9"/>
-        <v>-0.88859999999999884</v>
+        <v>-1.033599999999999</v>
       </c>
       <c r="N113">
         <f t="shared" ca="1" si="10"/>
-        <v>-1.6156363636363524</v>
+        <v>-1.8792727272727294</v>
       </c>
       <c r="O113">
         <f t="shared" ca="1" si="11"/>
-        <v>0.78960995999999795</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.0683289599999979</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D114" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>53.240300000000005</v>
+        <v>53.225300000000004</v>
       </c>
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
@@ -6106,29 +6106,29 @@
       </c>
       <c r="J114">
         <f t="shared" ca="1" si="14"/>
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="K114">
         <f t="shared" ca="1" si="15"/>
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="L114">
         <v>0.5</v>
       </c>
       <c r="M114">
         <f t="shared" ca="1" si="9"/>
-        <v>1.0402999999999989</v>
+        <v>1.0252999999999988</v>
       </c>
       <c r="N114">
         <f t="shared" ca="1" si="10"/>
-        <v>1.9929118773946319</v>
+        <v>1.9641762452107248</v>
       </c>
       <c r="O114">
         <f t="shared" ca="1" si="11"/>
-        <v>1.0822240899999978</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.0512400899999974</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="D115" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>30.393000000000001</v>
+        <v>31.402999999999999</v>
       </c>
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
@@ -6155,29 +6155,29 @@
       </c>
       <c r="J115">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.44</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K115">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.66</v>
+        <v>0.37</v>
       </c>
       <c r="L115">
         <v>0.5</v>
       </c>
       <c r="M115">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.1070000000000004</v>
+        <v>-9.7000000000000364E-2</v>
       </c>
       <c r="N115">
         <f t="shared" ca="1" si="10"/>
-        <v>-3.5142857142857142</v>
+        <v>-0.30793650793651262</v>
       </c>
       <c r="O115">
         <f t="shared" ca="1" si="11"/>
-        <v>1.2254490000000009</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+        <v>9.4090000000000701E-3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="D116" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>68.347850000000008</v>
+        <v>69.807850000000002</v>
       </c>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
@@ -6204,29 +6204,29 @@
       </c>
       <c r="J116">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.98</v>
+        <v>0.53</v>
       </c>
       <c r="K116">
         <f t="shared" ca="1" si="15"/>
-        <v>-1</v>
+        <v>0.41</v>
       </c>
       <c r="L116">
         <v>0.5</v>
       </c>
       <c r="M116">
         <f t="shared" ca="1" si="9"/>
-        <v>-2.6521499999999971</v>
+        <v>-1.1921499999999967</v>
       </c>
       <c r="N116">
         <f t="shared" ca="1" si="10"/>
-        <v>-3.7354225352112524</v>
+        <v>-1.67908450704225</v>
       </c>
       <c r="O116">
         <f t="shared" ca="1" si="11"/>
-        <v>7.0338996224999848</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.4212216224999921</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="D117" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>61.624250000000004</v>
+        <v>62.90925</v>
       </c>
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
@@ -6253,29 +6253,29 @@
       </c>
       <c r="J117">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.38</v>
+        <v>0.96</v>
       </c>
       <c r="K117">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.92</v>
+        <v>0.31</v>
       </c>
       <c r="L117">
         <v>0.5</v>
       </c>
       <c r="M117">
         <f t="shared" ca="1" si="9"/>
-        <v>3.6242500000000017</v>
+        <v>4.9092500000000028</v>
       </c>
       <c r="N117">
         <f t="shared" ca="1" si="10"/>
-        <v>6.2487068965517256</v>
+        <v>8.4642241379310423</v>
       </c>
       <c r="O117">
         <f t="shared" ca="1" si="11"/>
-        <v>13.135188062500013</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+        <v>24.100735562500027</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="D118" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>65.2898</v>
+        <v>65.099800000000002</v>
       </c>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
@@ -6302,29 +6302,29 @@
       </c>
       <c r="J118">
         <f t="shared" ca="1" si="14"/>
-        <v>0.2</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="K118">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.3</v>
+        <v>-0.19</v>
       </c>
       <c r="L118">
         <v>0.5</v>
       </c>
       <c r="M118">
         <f t="shared" ca="1" si="9"/>
-        <v>-0.1102000000000018</v>
+        <v>-0.3002000000000018</v>
       </c>
       <c r="N118">
         <f t="shared" ca="1" si="10"/>
-        <v>-0.16850152905200089</v>
+        <v>-0.45902140672783309</v>
       </c>
       <c r="O118">
         <f t="shared" ca="1" si="11"/>
-        <v>1.2144040000000396E-2</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+        <v>9.0120040000001081E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="D119" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>58.715350000000001</v>
+        <v>59.320349999999998</v>
       </c>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
@@ -6351,29 +6351,29 @@
       </c>
       <c r="J119">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.78</v>
+        <v>0.68</v>
       </c>
       <c r="K119">
         <f t="shared" ca="1" si="15"/>
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="L119">
         <v>0.5</v>
       </c>
       <c r="M119">
         <f t="shared" ca="1" si="9"/>
-        <v>-4.1846499999999986</v>
+        <v>-3.5796499999999987</v>
       </c>
       <c r="N119">
         <f t="shared" ca="1" si="10"/>
-        <v>-6.6528616852146278</v>
+        <v>-5.6910174880763105</v>
       </c>
       <c r="O119">
         <f t="shared" ca="1" si="11"/>
-        <v>17.51129562249999</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+        <v>12.81389412249999</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="D120" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>21.973749999999999</v>
+        <v>21.973050000000001</v>
       </c>
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
@@ -6400,29 +6400,29 @@
       </c>
       <c r="J120">
         <f t="shared" ca="1" si="14"/>
-        <v>-7.1000000000000004E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="K120">
         <f t="shared" ca="1" si="15"/>
-        <v>8.6E-3</v>
+        <v>-1.5E-3</v>
       </c>
       <c r="L120">
         <v>0.5</v>
       </c>
       <c r="M120">
         <f t="shared" ca="1" si="9"/>
-        <v>0.97375000000000067</v>
+        <v>0.97305000000000075</v>
       </c>
       <c r="N120">
         <f t="shared" ca="1" si="10"/>
-        <v>4.6369047619047477</v>
+        <v>4.6335714285714369</v>
       </c>
       <c r="O120">
         <f t="shared" ca="1" si="11"/>
-        <v>0.94818906250000135</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.94682630250000144</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>55.233350000000002</v>
+        <v>55.468350000000001</v>
       </c>
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
@@ -6449,29 +6449,29 @@
       </c>
       <c r="J121">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.24</v>
+        <v>0.69</v>
       </c>
       <c r="K121">
         <f t="shared" ca="1" si="15"/>
-        <v>0.94</v>
+        <v>0.48</v>
       </c>
       <c r="L121">
         <v>0.5</v>
       </c>
       <c r="M121">
         <f t="shared" ca="1" si="9"/>
-        <v>1.9333500000000028</v>
+        <v>2.1683500000000029</v>
       </c>
       <c r="N121">
         <f t="shared" ca="1" si="10"/>
-        <v>3.62729831144466</v>
+        <v>4.0681988742964359</v>
       </c>
       <c r="O121">
         <f t="shared" ca="1" si="11"/>
-        <v>3.737842222500011</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4.7017417225000129</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="D122" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>48.451299999999996</v>
+        <v>48.546300000000002</v>
       </c>
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
@@ -6498,29 +6498,29 @@
       </c>
       <c r="J122">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.54</v>
+        <v>0.16</v>
       </c>
       <c r="K122">
         <f t="shared" ca="1" si="15"/>
-        <v>0.71</v>
+        <v>0.2</v>
       </c>
       <c r="L122">
         <v>0.5</v>
       </c>
       <c r="M122">
         <f t="shared" ca="1" si="9"/>
-        <v>1.9512999999999989</v>
+        <v>2.0462999999999991</v>
       </c>
       <c r="N122">
         <f t="shared" ca="1" si="10"/>
-        <v>4.1963440860214973</v>
+        <v>4.4006451612903286</v>
       </c>
       <c r="O122">
         <f t="shared" ca="1" si="11"/>
-        <v>3.8075716899999956</v>
-      </c>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4.1873436899999961</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="D123" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>63.466300000000004</v>
+        <v>63.496299999999998</v>
       </c>
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
@@ -6547,29 +6547,29 @@
       </c>
       <c r="J123">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.44</v>
+        <v>-0.85</v>
       </c>
       <c r="K123">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.38</v>
+        <v>0.09</v>
       </c>
       <c r="L123">
         <v>0.5</v>
       </c>
       <c r="M123">
         <f t="shared" ca="1" si="9"/>
-        <v>0.66630000000000345</v>
+        <v>0.69630000000000336</v>
       </c>
       <c r="N123">
         <f t="shared" ca="1" si="10"/>
-        <v>1.0609872611465176</v>
+        <v>1.1087579617834464</v>
       </c>
       <c r="O123">
         <f t="shared" ca="1" si="11"/>
-        <v>0.44395569000000457</v>
-      </c>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.4848336900000047</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="D124" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>63.542149999999999</v>
+        <v>63.617150000000002</v>
       </c>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
@@ -6596,29 +6596,29 @@
       </c>
       <c r="J124">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.32</v>
+        <v>-0.63</v>
       </c>
       <c r="K124">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.63</v>
+        <v>-0.17</v>
       </c>
       <c r="L124">
         <v>0.5</v>
       </c>
       <c r="M124">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.157850000000002</v>
+        <v>-1.0828500000000019</v>
       </c>
       <c r="N124">
         <f t="shared" ca="1" si="10"/>
-        <v>-1.7895672333848589</v>
+        <v>-1.673647604327666</v>
       </c>
       <c r="O124">
         <f t="shared" ca="1" si="11"/>
-        <v>1.3406166225000047</v>
-      </c>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.1725641225000041</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="D125" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>22.55585</v>
+        <v>22.551199999999998</v>
       </c>
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
@@ -6645,29 +6645,29 @@
       </c>
       <c r="J125">
         <f t="shared" ca="1" si="14"/>
-        <v>6.4999999999999997E-3</v>
+        <v>-4.5999999999999999E-3</v>
       </c>
       <c r="K125">
         <f t="shared" ca="1" si="15"/>
-        <v>-4.0000000000000002E-4</v>
+        <v>1.4E-3</v>
       </c>
       <c r="L125">
         <v>0.5</v>
       </c>
       <c r="M125">
         <f t="shared" ca="1" si="9"/>
-        <v>0.7558499999999988</v>
+        <v>0.75119999999999887</v>
       </c>
       <c r="N125">
         <f t="shared" ca="1" si="10"/>
-        <v>3.4672018348623768</v>
+        <v>3.445871559633007</v>
       </c>
       <c r="O125">
         <f t="shared" ca="1" si="11"/>
-        <v>0.57130922249999816</v>
-      </c>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.56430143999999827</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="D126" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>60.972300000000004</v>
+        <v>61.482300000000002</v>
       </c>
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
@@ -6694,29 +6694,29 @@
       </c>
       <c r="J126">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.54</v>
+        <v>0.47</v>
       </c>
       <c r="K126">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="L126">
         <v>0.5</v>
       </c>
       <c r="M126">
         <f t="shared" ca="1" si="9"/>
-        <v>1.2722999999999993</v>
+        <v>1.7822999999999991</v>
       </c>
       <c r="N126">
         <f t="shared" ca="1" si="10"/>
-        <v>2.1311557788944668</v>
+        <v>2.9854271356783979</v>
       </c>
       <c r="O126">
         <f t="shared" ca="1" si="11"/>
-        <v>1.6187472899999982</v>
-      </c>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+        <v>3.1765932899999969</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="D127" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>78.605350000000001</v>
+        <v>79.275350000000003</v>
       </c>
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
@@ -6743,29 +6743,29 @@
       </c>
       <c r="J127">
         <f t="shared" ca="1" si="14"/>
-        <v>0.59</v>
+        <v>0.94</v>
       </c>
       <c r="K127">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.33</v>
+        <v>0.66</v>
       </c>
       <c r="L127">
         <v>0.5</v>
       </c>
       <c r="M127">
         <f t="shared" ca="1" si="9"/>
-        <v>-1.6946499999999984</v>
+        <v>-1.0246499999999983</v>
       </c>
       <c r="N127">
         <f t="shared" ca="1" si="10"/>
-        <v>-2.1103985056039831</v>
+        <v>-1.2760273972602709</v>
       </c>
       <c r="O127">
         <f t="shared" ca="1" si="11"/>
-        <v>2.8718386224999946</v>
-      </c>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.0499076224999966</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="D128" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>68.711849999999998</v>
+        <v>68.386849999999995</v>
       </c>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
@@ -6792,29 +6792,29 @@
       </c>
       <c r="J128">
         <f t="shared" ca="1" si="14"/>
-        <v>0.38</v>
+        <v>-0.46</v>
       </c>
       <c r="K128">
         <f t="shared" ca="1" si="15"/>
-        <v>-0.3</v>
+        <v>-0.11</v>
       </c>
       <c r="L128">
         <v>0.5</v>
       </c>
       <c r="M128">
         <f t="shared" ca="1" si="9"/>
-        <v>0.71184999999999909</v>
+        <v>0.38684999999999919</v>
       </c>
       <c r="N128">
         <f t="shared" ca="1" si="10"/>
-        <v>1.046838235294123</v>
+        <v>0.56889705882352537</v>
       </c>
       <c r="O128">
         <f t="shared" ca="1" si="11"/>
-        <v>0.50673042249999867</v>
-      </c>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.14965292249999937</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D129" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>58.571199999999997</v>
+        <v>58.911200000000001</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -6841,29 +6841,29 @@
       </c>
       <c r="J129">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.96</v>
+        <v>0.7</v>
       </c>
       <c r="K129">
         <f t="shared" ca="1" si="15"/>
-        <v>0.84</v>
+        <v>-0.14000000000000001</v>
       </c>
       <c r="L129">
         <v>0.5</v>
       </c>
       <c r="M129">
         <f t="shared" ca="1" si="9"/>
-        <v>2.0711999999999997</v>
+        <v>2.4112</v>
       </c>
       <c r="N129">
         <f t="shared" ca="1" si="10"/>
-        <v>3.6658407079646071</v>
+        <v>4.2676106194690311</v>
       </c>
       <c r="O129">
         <f t="shared" ca="1" si="11"/>
-        <v>4.2898694399999986</v>
-      </c>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+        <v>5.81388544</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="D130" s="4">
         <f t="shared" ca="1" si="8"/>
-        <v>80.844999999999999</v>
+        <v>80.375</v>
       </c>
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
@@ -6890,29 +6890,29 @@
       </c>
       <c r="J130">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.56999999999999995</v>
+        <v>-0.16</v>
       </c>
       <c r="K130">
         <f t="shared" ca="1" si="15"/>
-        <v>1</v>
+        <v>-0.35</v>
       </c>
       <c r="L130">
         <v>0.5</v>
       </c>
       <c r="M130">
         <f t="shared" ca="1" si="9"/>
-        <v>-3.3550000000000004</v>
+        <v>-3.8250000000000002</v>
       </c>
       <c r="N130">
         <f t="shared" ca="1" si="10"/>
-        <v>-3.9845605700712605</v>
+        <v>-4.5427553444180591</v>
       </c>
       <c r="O130">
         <f t="shared" ca="1" si="11"/>
-        <v>11.256025000000003</v>
-      </c>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+        <v>14.630625000000002</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="D131" s="4">
         <f t="shared" ref="D131:D194" ca="1" si="16">B131+M131</f>
-        <v>70.161450000000002</v>
+        <v>69.466449999999995</v>
       </c>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
@@ -6939,29 +6939,29 @@
       </c>
       <c r="J131">
         <f t="shared" ca="1" si="14"/>
-        <v>-0.49</v>
+        <v>-1</v>
       </c>
       <c r="K131">
         <f t="shared" ca="1" si="15"/>
-        <v>0.26</v>
+        <v>-0.62</v>
       </c>
       <c r="L131">
         <v>0.5</v>
       </c>
       <c r="M131">
         <f t="shared" ref="M131:M194" ca="1" si="17">(I131+J131+K131)*L131</f>
-        <v>-0.63855000000000017</v>
+        <v>-1.3335500000000002</v>
       </c>
       <c r="N131">
         <f t="shared" ref="N131:N194" ca="1" si="18">((D131/B131)-1)*100</f>
-        <v>-0.90190677966101029</v>
+        <v>-1.8835451977401219</v>
       </c>
       <c r="O131">
         <f t="shared" ref="O131:O194" ca="1" si="19">M131^2</f>
-        <v>0.40774610250000021</v>
-      </c>
-    </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.7783556025000007</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="D132" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>70.953450000000004</v>
+        <v>70.343450000000004</v>
       </c>
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
@@ -6988,29 +6988,29 @@
       </c>
       <c r="J132">
         <f t="shared" ref="J132:J195" ca="1" si="22">IF(B132 &lt; 30, RANDBETWEEN(-100, 100) / 10000, RANDBETWEEN(-100,100) / 100)</f>
-        <v>0.96</v>
+        <v>0.79</v>
       </c>
       <c r="K132">
         <f t="shared" ref="K132:K195" ca="1" si="23">IF(B132 &lt; 30, RANDBETWEEN(-100, 100) / 10000, RANDBETWEEN(-100,100) / 100)</f>
-        <v>0.43</v>
+        <v>-0.62</v>
       </c>
       <c r="L132">
         <v>0.5</v>
       </c>
       <c r="M132">
         <f t="shared" ca="1" si="17"/>
-        <v>-0.74654999999999949</v>
+        <v>-1.3565499999999995</v>
       </c>
       <c r="N132">
         <f t="shared" ca="1" si="18"/>
-        <v>-1.0412133891213426</v>
+        <v>-1.8919804741980406</v>
       </c>
       <c r="O132">
         <f t="shared" ca="1" si="19"/>
-        <v>0.55733690249999923</v>
-      </c>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.8402279024999986</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="D133" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>26.473299999999998</v>
+        <v>26.470649999999999</v>
       </c>
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
@@ -7037,29 +7037,29 @@
       </c>
       <c r="J133">
         <f t="shared" ca="1" si="22"/>
-        <v>1E-4</v>
+        <v>-5.4000000000000003E-3</v>
       </c>
       <c r="K133">
         <f t="shared" ca="1" si="23"/>
-        <v>-8.9999999999999993E-3</v>
+        <v>-8.8000000000000005E-3</v>
       </c>
       <c r="L133">
         <v>0.5</v>
       </c>
       <c r="M133">
         <f t="shared" ca="1" si="17"/>
-        <v>0.73330000000000017</v>
+        <v>0.73065000000000013</v>
       </c>
       <c r="N133">
         <f t="shared" ca="1" si="18"/>
-        <v>2.8488733488733375</v>
+        <v>2.8385780885780809</v>
       </c>
       <c r="O133">
         <f t="shared" ca="1" si="19"/>
-        <v>0.53772889000000024</v>
-      </c>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.53384942250000023</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="D134" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>40.724899999999998</v>
+        <v>40.219900000000003</v>
       </c>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
@@ -7086,29 +7086,29 @@
       </c>
       <c r="J134">
         <f t="shared" ca="1" si="22"/>
-        <v>-0.65</v>
+        <v>-0.99</v>
       </c>
       <c r="K134">
         <f t="shared" ca="1" si="23"/>
-        <v>0.71</v>
+        <v>0.04</v>
       </c>
       <c r="L134">
         <v>0.5</v>
       </c>
       <c r="M134">
         <f t="shared" ca="1" si="17"/>
-        <v>0.37489999999999907</v>
+        <v>-0.13010000000000091</v>
       </c>
       <c r="N134">
         <f t="shared" ca="1" si="18"/>
-        <v>0.92912019826516534</v>
+        <v>-0.32242874845105352</v>
       </c>
       <c r="O134">
         <f t="shared" ca="1" si="19"/>
-        <v>0.14055000999999931</v>
-      </c>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.6926010000000238E-2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="D135" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>33.222050000000003</v>
+        <v>32.95205</v>
       </c>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
@@ -7135,29 +7135,29 @@
       </c>
       <c r="J135">
         <f t="shared" ca="1" si="22"/>
-        <v>-1</v>
+        <v>0.18</v>
       </c>
       <c r="K135">
         <f t="shared" ca="1" si="23"/>
-        <v>0.88</v>
+        <v>-0.84</v>
       </c>
       <c r="L135">
         <v>0.5</v>
       </c>
       <c r="M135">
         <f t="shared" ca="1" si="17"/>
-        <v>-1.2779499999999984</v>
+        <v>-1.5479499999999982</v>
       </c>
       <c r="N135">
         <f t="shared" ca="1" si="18"/>
-        <v>-3.7042028985507125</v>
+        <v>-4.4868115942028997</v>
       </c>
       <c r="O135">
         <f t="shared" ca="1" si="19"/>
-        <v>1.6331562024999957</v>
-      </c>
-    </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2.3961492024999944</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="D136" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>20.474399999999999</v>
+        <v>20.473399999999998</v>
       </c>
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
@@ -7184,29 +7184,29 @@
       </c>
       <c r="J136">
         <f t="shared" ca="1" si="22"/>
-        <v>-9.1999999999999998E-3</v>
+        <v>-8.8000000000000005E-3</v>
       </c>
       <c r="K136">
         <f t="shared" ca="1" si="23"/>
-        <v>-3.0999999999999999E-3</v>
+        <v>-5.4999999999999997E-3</v>
       </c>
       <c r="L136">
         <v>0.5</v>
       </c>
       <c r="M136">
         <f t="shared" ca="1" si="17"/>
-        <v>-0.52560000000000096</v>
+        <v>-0.52660000000000085</v>
       </c>
       <c r="N136">
         <f t="shared" ca="1" si="18"/>
-        <v>-2.5028571428571511</v>
+        <v>-2.5076190476190585</v>
       </c>
       <c r="O136">
         <f t="shared" ca="1" si="19"/>
-        <v>0.276255360000001</v>
-      </c>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.2773075600000009</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="D137" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>44.304299999999998</v>
+        <v>44.769300000000001</v>
       </c>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
@@ -7233,29 +7233,29 @@
       </c>
       <c r="J137">
         <f t="shared" ca="1" si="22"/>
-        <v>-0.06</v>
+        <v>0.41</v>
       </c>
       <c r="K137">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.17</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="L137">
         <v>0.5</v>
       </c>
       <c r="M137">
         <f t="shared" ca="1" si="17"/>
-        <v>0.30429999999999974</v>
+        <v>0.76929999999999976</v>
       </c>
       <c r="N137">
         <f t="shared" ca="1" si="18"/>
-        <v>0.69159090909090004</v>
+        <v>1.7484090909090977</v>
       </c>
       <c r="O137">
         <f t="shared" ca="1" si="19"/>
-        <v>9.2598489999999839E-2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.59182248999999965</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="D138" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>27.285499999999999</v>
+        <v>27.28145</v>
       </c>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
@@ -7282,29 +7282,29 @@
       </c>
       <c r="J138">
         <f t="shared" ca="1" si="22"/>
-        <v>9.9000000000000008E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="K138">
         <f t="shared" ca="1" si="23"/>
-        <v>-2.0000000000000001E-4</v>
+        <v>1E-4</v>
       </c>
       <c r="L138">
         <v>0.5</v>
       </c>
       <c r="M138">
         <f t="shared" ca="1" si="17"/>
-        <v>0.28549999999999964</v>
+        <v>0.28144999999999959</v>
       </c>
       <c r="N138">
         <f t="shared" ca="1" si="18"/>
-        <v>1.0574074074074069</v>
+        <v>1.0424074074073975</v>
       </c>
       <c r="O138">
         <f t="shared" ca="1" si="19"/>
-        <v>8.1510249999999798E-2</v>
-      </c>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+        <v>7.9214102499999772E-2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>137</v>
       </c>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="D139" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>7.8534449999999998</v>
+        <v>7.854895</v>
       </c>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
@@ -7331,29 +7331,29 @@
       </c>
       <c r="J139">
         <f t="shared" ca="1" si="22"/>
-        <v>6.7000000000000002E-3</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="K139">
         <f t="shared" ca="1" si="23"/>
-        <v>1.6999999999999999E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="L139">
         <v>0.5</v>
       </c>
       <c r="M139">
         <f t="shared" ca="1" si="17"/>
-        <v>0.35344499999999984</v>
+        <v>0.35489499999999979</v>
       </c>
       <c r="N139">
         <f t="shared" ca="1" si="18"/>
-        <v>4.7126000000000001</v>
+        <v>4.7319333333333269</v>
       </c>
       <c r="O139">
         <f t="shared" ca="1" si="19"/>
-        <v>0.12492336802499988</v>
-      </c>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.12595046102499985</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>138</v>
       </c>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="D140" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>32.931249999999999</v>
+        <v>32.426249999999996</v>
       </c>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
@@ -7380,29 +7380,29 @@
       </c>
       <c r="J140">
         <f t="shared" ca="1" si="22"/>
-        <v>0.42</v>
+        <v>-0.49</v>
       </c>
       <c r="K140">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.49</v>
+        <v>-0.59</v>
       </c>
       <c r="L140">
         <v>0.5</v>
       </c>
       <c r="M140">
         <f t="shared" ca="1" si="17"/>
-        <v>0.93124999999999869</v>
+        <v>0.42624999999999874</v>
       </c>
       <c r="N140">
         <f t="shared" ca="1" si="18"/>
-        <v>2.9101562499999956</v>
+        <v>1.3320312499999876</v>
       </c>
       <c r="O140">
         <f t="shared" ca="1" si="19"/>
-        <v>0.86722656249999752</v>
-      </c>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.18168906249999892</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>139</v>
       </c>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="D141" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>29.821950000000001</v>
+        <v>30.20195</v>
       </c>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
@@ -7429,29 +7429,29 @@
       </c>
       <c r="J141">
         <f t="shared" ca="1" si="22"/>
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="K141">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.23</v>
+        <v>0.42</v>
       </c>
       <c r="L141">
         <v>0.5</v>
       </c>
       <c r="M141">
         <f t="shared" ca="1" si="17"/>
-        <v>-0.17804999999999993</v>
+        <v>0.20195000000000007</v>
       </c>
       <c r="N141">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.59349999999999126</v>
+        <v>0.67316666666665803</v>
       </c>
       <c r="O141">
         <f t="shared" ca="1" si="19"/>
-        <v>3.1701802499999973E-2</v>
-      </c>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4.0783802500000028E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>140</v>
       </c>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="D142" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>8.6237049999999993</v>
+        <v>8.618055</v>
       </c>
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
@@ -7478,29 +7478,29 @@
       </c>
       <c r="J142">
         <f t="shared" ca="1" si="22"/>
-        <v>-3.3999999999999998E-3</v>
+        <v>-7.4999999999999997E-3</v>
       </c>
       <c r="K142">
         <f t="shared" ca="1" si="23"/>
-        <v>5.5999999999999999E-3</v>
+        <v>-1.6000000000000001E-3</v>
       </c>
       <c r="L142">
         <v>0.5</v>
       </c>
       <c r="M142">
         <f t="shared" ca="1" si="17"/>
-        <v>0.12370500000000008</v>
+        <v>0.11805500000000008</v>
       </c>
       <c r="N142">
         <f t="shared" ca="1" si="18"/>
-        <v>1.4553529411764687</v>
+        <v>1.3888823529411676</v>
       </c>
       <c r="O142">
         <f t="shared" ca="1" si="19"/>
-        <v>1.530292702500002E-2</v>
-      </c>
-    </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.3936983025000018E-2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>141</v>
       </c>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="D143" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>69.50030000000001</v>
+        <v>69.985300000000009</v>
       </c>
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
@@ -7527,29 +7527,29 @@
       </c>
       <c r="J143">
         <f t="shared" ca="1" si="22"/>
-        <v>-7.0000000000000007E-2</v>
+        <v>-0.08</v>
       </c>
       <c r="K143">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.33</v>
+        <v>0.65</v>
       </c>
       <c r="L143">
         <v>0.5</v>
       </c>
       <c r="M143">
         <f t="shared" ca="1" si="17"/>
-        <v>-0.36969999999999886</v>
+        <v>0.11530000000000115</v>
       </c>
       <c r="N143">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.52912551882066117</v>
+        <v>0.16502075282669448</v>
       </c>
       <c r="O143">
         <f t="shared" ca="1" si="19"/>
-        <v>0.13667808999999917</v>
-      </c>
-    </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.3294090000000265E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>142</v>
       </c>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="D144" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>49.067799999999998</v>
+        <v>48.907799999999995</v>
       </c>
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="J144">
         <f t="shared" ca="1" si="22"/>
-        <v>0.5</v>
+        <v>0.18</v>
       </c>
       <c r="K144">
         <f t="shared" ca="1" si="23"/>
@@ -7587,18 +7587,18 @@
       </c>
       <c r="M144">
         <f t="shared" ca="1" si="17"/>
-        <v>0.27779999999999871</v>
+        <v>0.11779999999999871</v>
       </c>
       <c r="N144">
         <f t="shared" ca="1" si="18"/>
-        <v>0.5693789711006314</v>
+        <v>0.24144291863086309</v>
       </c>
       <c r="O144">
         <f t="shared" ca="1" si="19"/>
-        <v>7.7172839999999285E-2</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.3876839999999696E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>143</v>
       </c>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="D145" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>27.624500000000001</v>
+        <v>27.616150000000001</v>
       </c>
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
@@ -7625,29 +7625,29 @@
       </c>
       <c r="J145">
         <f t="shared" ca="1" si="22"/>
-        <v>9.7000000000000003E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="K145">
         <f t="shared" ca="1" si="23"/>
-        <v>4.3E-3</v>
+        <v>-4.4999999999999997E-3</v>
       </c>
       <c r="L145">
         <v>0.5</v>
       </c>
       <c r="M145">
         <f t="shared" ca="1" si="17"/>
-        <v>0.24450000000000072</v>
+        <v>0.23615000000000072</v>
       </c>
       <c r="N145">
         <f t="shared" ca="1" si="18"/>
-        <v>0.8929875821767741</v>
+        <v>0.86249086924763407</v>
       </c>
       <c r="O145">
         <f t="shared" ca="1" si="19"/>
-        <v>5.9780250000000354E-2</v>
-      </c>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+        <v>5.576682250000034E-2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>144</v>
       </c>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="D146" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>69.940349999999995</v>
+        <v>69.315349999999995</v>
       </c>
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
@@ -7674,29 +7674,29 @@
       </c>
       <c r="J146">
         <f t="shared" ca="1" si="22"/>
-        <v>-0.21</v>
+        <v>-0.86</v>
       </c>
       <c r="K146">
         <f t="shared" ca="1" si="23"/>
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="L146">
         <v>0.5</v>
       </c>
       <c r="M146">
         <f t="shared" ca="1" si="17"/>
-        <v>8.0350000000002531E-2</v>
+        <v>-0.54464999999999741</v>
       </c>
       <c r="N146">
         <f t="shared" ca="1" si="18"/>
-        <v>0.11501574577725826</v>
+        <v>-0.77963068995133833</v>
       </c>
       <c r="O146">
         <f t="shared" ca="1" si="19"/>
-        <v>6.4561225000004064E-3</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.29664362249999721</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>145</v>
       </c>
@@ -7708,7 +7708,7 @@
       </c>
       <c r="D147" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>47.174349999999997</v>
+        <v>48.12435</v>
       </c>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
@@ -7723,29 +7723,29 @@
       </c>
       <c r="J147">
         <f t="shared" ca="1" si="22"/>
-        <v>-0.96</v>
+        <v>0.78</v>
       </c>
       <c r="K147">
         <f t="shared" ca="1" si="23"/>
-        <v>0.34</v>
+        <v>0.5</v>
       </c>
       <c r="L147">
         <v>0.5</v>
       </c>
       <c r="M147">
         <f t="shared" ca="1" si="17"/>
-        <v>0.10434999999999892</v>
+        <v>1.054349999999999</v>
       </c>
       <c r="N147">
         <f t="shared" ca="1" si="18"/>
-        <v>0.22169109836414069</v>
+        <v>2.2399617590822096</v>
       </c>
       <c r="O147">
         <f t="shared" ca="1" si="19"/>
-        <v>1.0888922499999773E-2</v>
-      </c>
-    </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.1116539224999979</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>146</v>
       </c>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="D148" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>25.0688</v>
+        <v>25.070350000000001</v>
       </c>
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
@@ -7772,29 +7772,29 @@
       </c>
       <c r="J148">
         <f t="shared" ca="1" si="22"/>
-        <v>-4.7999999999999996E-3</v>
+        <v>-4.4999999999999997E-3</v>
       </c>
       <c r="K148">
         <f t="shared" ca="1" si="23"/>
-        <v>6.8999999999999999E-3</v>
+        <v>9.7000000000000003E-3</v>
       </c>
       <c r="L148">
         <v>0.5</v>
       </c>
       <c r="M148">
         <f t="shared" ca="1" si="17"/>
-        <v>2.7487999999999997</v>
+        <v>2.7503499999999996</v>
       </c>
       <c r="N148">
         <f t="shared" ca="1" si="18"/>
-        <v>12.315412186379927</v>
+        <v>12.322356630824371</v>
       </c>
       <c r="O148">
         <f t="shared" ca="1" si="19"/>
-        <v>7.5559014399999986</v>
-      </c>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+        <v>7.5644251224999977</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>147</v>
       </c>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="D149" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>89.742949999999993</v>
+        <v>89.522949999999994</v>
       </c>
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
@@ -7821,29 +7821,29 @@
       </c>
       <c r="J149">
         <f t="shared" ca="1" si="22"/>
-        <v>0.56999999999999995</v>
+        <v>-0.14000000000000001</v>
       </c>
       <c r="K149">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="L149">
         <v>0.5</v>
       </c>
       <c r="M149">
         <f t="shared" ca="1" si="17"/>
-        <v>-1.4970499999999969</v>
+        <v>-1.7170499999999969</v>
       </c>
       <c r="N149">
         <f t="shared" ca="1" si="18"/>
-        <v>-1.6407825515124985</v>
+        <v>-1.881904866286721</v>
       </c>
       <c r="O149">
         <f t="shared" ca="1" si="19"/>
-        <v>2.2411587024999906</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2.9482607024999892</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>148</v>
       </c>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="D150" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>71.324200000000005</v>
+        <v>72.554199999999994</v>
       </c>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
@@ -7870,29 +7870,29 @@
       </c>
       <c r="J150">
         <f t="shared" ca="1" si="22"/>
-        <v>-0.46</v>
+        <v>0.21</v>
       </c>
       <c r="K150">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.93</v>
+        <v>0.86</v>
       </c>
       <c r="L150">
         <v>0.5</v>
       </c>
       <c r="M150">
         <f t="shared" ca="1" si="17"/>
-        <v>2.1241999999999952</v>
+        <v>3.3541999999999952</v>
       </c>
       <c r="N150">
         <f t="shared" ca="1" si="18"/>
-        <v>3.0696531791907455</v>
+        <v>4.8471098265895796</v>
       </c>
       <c r="O150">
         <f t="shared" ca="1" si="19"/>
-        <v>4.5122256399999801</v>
-      </c>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+        <v>11.250657639999968</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>149</v>
       </c>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="D151" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>66.317300000000003</v>
+        <v>66.572299999999998</v>
       </c>
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
@@ -7919,29 +7919,29 @@
       </c>
       <c r="J151">
         <f t="shared" ca="1" si="22"/>
-        <v>-0.17</v>
+        <v>0.3</v>
       </c>
       <c r="K151">
         <f t="shared" ca="1" si="23"/>
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="L151">
         <v>0.5</v>
       </c>
       <c r="M151">
         <f t="shared" ca="1" si="17"/>
-        <v>-0.58270000000000122</v>
+        <v>-0.32770000000000121</v>
       </c>
       <c r="N151">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.87100149476831978</v>
+        <v>-0.48983557548580858</v>
       </c>
       <c r="O151">
         <f t="shared" ca="1" si="19"/>
-        <v>0.33953929000000144</v>
-      </c>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.1073872900000008</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>150</v>
       </c>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="D152" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>40.309350000000002</v>
+        <v>39.589350000000003</v>
       </c>
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
@@ -7968,29 +7968,29 @@
       </c>
       <c r="J152">
         <f t="shared" ca="1" si="22"/>
-        <v>0.59</v>
+        <v>-0.74</v>
       </c>
       <c r="K152">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.25</v>
+        <v>-0.36</v>
       </c>
       <c r="L152">
         <v>0.5</v>
       </c>
       <c r="M152">
         <f t="shared" ca="1" si="17"/>
-        <v>2.4093500000000017</v>
+        <v>1.6893500000000017</v>
       </c>
       <c r="N152">
         <f t="shared" ca="1" si="18"/>
-        <v>6.3571240105541049</v>
+        <v>4.4573878627968355</v>
       </c>
       <c r="O152">
         <f t="shared" ca="1" si="19"/>
-        <v>5.8049674225000079</v>
-      </c>
-    </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2.8539034225000055</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>151</v>
       </c>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="D153" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>35.23995</v>
+        <v>35.237099999999998</v>
       </c>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
@@ -8017,29 +8017,29 @@
       </c>
       <c r="J153">
         <f t="shared" ca="1" si="22"/>
-        <v>-7.9000000000000008E-3</v>
+        <v>-6.4000000000000003E-3</v>
       </c>
       <c r="K153">
         <f t="shared" ca="1" si="23"/>
-        <v>9.1999999999999998E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="L153">
         <v>0.5</v>
       </c>
       <c r="M153">
         <f t="shared" ca="1" si="17"/>
-        <v>5.8399500000000018</v>
+        <v>5.8371000000000022</v>
       </c>
       <c r="N153">
         <f t="shared" ca="1" si="18"/>
-        <v>19.863775510204086</v>
+        <v>19.854081632653052</v>
       </c>
       <c r="O153">
         <f t="shared" ca="1" si="19"/>
-        <v>34.105016002500022</v>
-      </c>
-    </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+        <v>34.071736410000028</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>152</v>
       </c>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="D154" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>68.485849999999999</v>
+        <v>68.525850000000005</v>
       </c>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
@@ -8066,29 +8066,29 @@
       </c>
       <c r="J154">
         <f t="shared" ca="1" si="22"/>
-        <v>0.03</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="K154">
         <f t="shared" ca="1" si="23"/>
-        <v>0.79</v>
+        <v>0.34</v>
       </c>
       <c r="L154">
         <v>0.5</v>
       </c>
       <c r="M154">
         <f t="shared" ca="1" si="17"/>
-        <v>-2.7141500000000001</v>
+        <v>-2.67415</v>
       </c>
       <c r="N154">
         <f t="shared" ca="1" si="18"/>
-        <v>-3.8120084269662957</v>
+        <v>-3.7558286516853889</v>
       </c>
       <c r="O154">
         <f t="shared" ca="1" si="19"/>
-        <v>7.3666102225000003</v>
-      </c>
-    </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+        <v>7.1510782224999998</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>153</v>
       </c>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="D155" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>51.374949999999998</v>
+        <v>51.534950000000002</v>
       </c>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
@@ -8115,29 +8115,29 @@
       </c>
       <c r="J155">
         <f t="shared" ca="1" si="22"/>
-        <v>0.26</v>
+        <v>0.82</v>
       </c>
       <c r="K155">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.55000000000000004</v>
+        <v>-0.79</v>
       </c>
       <c r="L155">
         <v>0.5</v>
       </c>
       <c r="M155">
         <f t="shared" ca="1" si="17"/>
-        <v>0.37495000000000145</v>
+        <v>0.53495000000000137</v>
       </c>
       <c r="N155">
         <f t="shared" ca="1" si="18"/>
-        <v>0.73519607843137713</v>
+        <v>1.0489215686274589</v>
       </c>
       <c r="O155">
         <f t="shared" ca="1" si="19"/>
-        <v>0.1405875025000011</v>
-      </c>
-    </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.28617150250000145</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>154</v>
       </c>
@@ -8149,7 +8149,7 @@
       </c>
       <c r="D156" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>34.752650000000003</v>
+        <v>34.707650000000001</v>
       </c>
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
@@ -8164,29 +8164,29 @@
       </c>
       <c r="J156">
         <f t="shared" ca="1" si="22"/>
-        <v>-0.7</v>
+        <v>-0.69</v>
       </c>
       <c r="K156">
         <f t="shared" ca="1" si="23"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L156">
         <v>0.5</v>
       </c>
       <c r="M156">
         <f t="shared" ca="1" si="17"/>
-        <v>2.7526499999999992</v>
+        <v>2.7076499999999992</v>
       </c>
       <c r="N156">
         <f t="shared" ca="1" si="18"/>
-        <v>8.6020312500000085</v>
+        <v>8.4614062500000031</v>
       </c>
       <c r="O156">
         <f t="shared" ca="1" si="19"/>
-        <v>7.5770820224999955</v>
-      </c>
-    </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+        <v>7.3313685224999956</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>155</v>
       </c>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="D157" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>25.533750000000001</v>
+        <v>25.541599999999999</v>
       </c>
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
@@ -8213,29 +8213,29 @@
       </c>
       <c r="J157">
         <f t="shared" ca="1" si="22"/>
-        <v>-3.2000000000000002E-3</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="K157">
         <f t="shared" ca="1" si="23"/>
-        <v>2.0000000000000001E-4</v>
+        <v>7.3000000000000001E-3</v>
       </c>
       <c r="L157">
         <v>0.5</v>
       </c>
       <c r="M157">
         <f t="shared" ca="1" si="17"/>
-        <v>-2.4662500000000001</v>
+        <v>-2.4584000000000006</v>
       </c>
       <c r="N157">
         <f t="shared" ca="1" si="18"/>
-        <v>-8.8080357142857117</v>
+        <v>-8.7799999999999994</v>
       </c>
       <c r="O157">
         <f t="shared" ca="1" si="19"/>
-        <v>6.0823890624999999</v>
-      </c>
-    </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+        <v>6.0437305600000029</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>156</v>
       </c>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="D158" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>35.946250000000006</v>
+        <v>35.691250000000004</v>
       </c>
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
@@ -8262,29 +8262,29 @@
       </c>
       <c r="J158">
         <f t="shared" ca="1" si="22"/>
-        <v>0.66</v>
+        <v>-0.14000000000000001</v>
       </c>
       <c r="K158">
         <f t="shared" ca="1" si="23"/>
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="L158">
         <v>0.5</v>
       </c>
       <c r="M158">
         <f t="shared" ca="1" si="17"/>
-        <v>-1.2537499999999997</v>
+        <v>-1.5087499999999998</v>
       </c>
       <c r="N158">
         <f t="shared" ca="1" si="18"/>
-        <v>-3.370295698924719</v>
+        <v>-4.0557795698924703</v>
       </c>
       <c r="O158">
         <f t="shared" ca="1" si="19"/>
-        <v>1.5718890624999993</v>
-      </c>
-    </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2.2763265624999995</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>157</v>
       </c>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="D159" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>74.661950000000004</v>
+        <v>75.091949999999997</v>
       </c>
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
@@ -8311,29 +8311,29 @@
       </c>
       <c r="J159">
         <f t="shared" ca="1" si="22"/>
-        <v>-0.69</v>
+        <v>-0.11</v>
       </c>
       <c r="K159">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.56999999999999995</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="L159">
         <v>0.5</v>
       </c>
       <c r="M159">
         <f t="shared" ca="1" si="17"/>
-        <v>1.8619500000000031</v>
+        <v>2.2919500000000026</v>
       </c>
       <c r="N159">
         <f t="shared" ca="1" si="18"/>
-        <v>2.5576236263736396</v>
+        <v>3.1482829670329782</v>
       </c>
       <c r="O159">
         <f t="shared" ca="1" si="19"/>
-        <v>3.4668578025000114</v>
-      </c>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+        <v>5.2530348025000118</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>158</v>
       </c>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="D160" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>92.114149999999995</v>
+        <v>92.574150000000003</v>
       </c>
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
@@ -8360,29 +8360,29 @@
       </c>
       <c r="J160">
         <f t="shared" ca="1" si="22"/>
-        <v>0.24</v>
+        <v>-0.01</v>
       </c>
       <c r="K160">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.57999999999999996</v>
+        <v>0.59</v>
       </c>
       <c r="L160">
         <v>0.5</v>
       </c>
       <c r="M160">
         <f t="shared" ca="1" si="17"/>
-        <v>-3.1858500000000003</v>
+        <v>-2.7258500000000003</v>
       </c>
       <c r="N160">
         <f t="shared" ca="1" si="18"/>
-        <v>-3.3429695697796413</v>
+        <v>-2.8602833158446916</v>
       </c>
       <c r="O160">
         <f t="shared" ca="1" si="19"/>
-        <v>10.149640222500002</v>
-      </c>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+        <v>7.4302582225000018</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>159</v>
       </c>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="D161" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>73.103250000000003</v>
+        <v>72.703249999999997</v>
       </c>
       <c r="E161" s="1"/>
       <c r="F161" s="1"/>
@@ -8409,29 +8409,29 @@
       </c>
       <c r="J161">
         <f t="shared" ca="1" si="22"/>
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="K161">
         <f t="shared" ca="1" si="23"/>
-        <v>0.26</v>
+        <v>-0.49</v>
       </c>
       <c r="L161">
         <v>0.5</v>
       </c>
       <c r="M161">
         <f t="shared" ca="1" si="17"/>
-        <v>-2.3967500000000017</v>
+        <v>-2.7967500000000016</v>
       </c>
       <c r="N161">
         <f t="shared" ca="1" si="18"/>
-        <v>-3.1745033112582699</v>
+        <v>-3.7043046357615905</v>
       </c>
       <c r="O161">
         <f t="shared" ca="1" si="19"/>
-        <v>5.7444105625000086</v>
-      </c>
-    </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+        <v>7.8218105625000094</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>160</v>
       </c>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="D162" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>73.579900000000009</v>
+        <v>73.494900000000001</v>
       </c>
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
@@ -8458,29 +8458,29 @@
       </c>
       <c r="J162">
         <f t="shared" ca="1" si="22"/>
-        <v>-0.74</v>
+        <v>0.8</v>
       </c>
       <c r="K162">
         <f t="shared" ca="1" si="23"/>
-        <v>0.74</v>
+        <v>-0.97</v>
       </c>
       <c r="L162">
         <v>0.5</v>
       </c>
       <c r="M162">
         <f t="shared" ca="1" si="17"/>
-        <v>-0.12010000000000076</v>
+        <v>-0.20510000000000073</v>
       </c>
       <c r="N162">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.1629579375847956</v>
+        <v>-0.27829036635006466</v>
       </c>
       <c r="O162">
         <f t="shared" ca="1" si="19"/>
-        <v>1.4424010000000183E-2</v>
-      </c>
-    </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4.2066010000000299E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>161</v>
       </c>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="D163" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>74.415149999999997</v>
+        <v>74.260149999999996</v>
       </c>
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
@@ -8507,29 +8507,29 @@
       </c>
       <c r="J163">
         <f t="shared" ca="1" si="22"/>
-        <v>0.08</v>
+        <v>0.48</v>
       </c>
       <c r="K163">
         <f t="shared" ca="1" si="23"/>
-        <v>0.6</v>
+        <v>-0.11</v>
       </c>
       <c r="L163">
         <v>0.5</v>
       </c>
       <c r="M163">
         <f t="shared" ca="1" si="17"/>
-        <v>1.0151499999999951</v>
+        <v>0.86014999999999497</v>
       </c>
       <c r="N163">
         <f t="shared" ca="1" si="18"/>
-        <v>1.3830381471389597</v>
+        <v>1.1718664850136173</v>
       </c>
       <c r="O163">
         <f t="shared" ca="1" si="19"/>
-        <v>1.03052952249999</v>
-      </c>
-    </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.73985802249999133</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>162</v>
       </c>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="D164" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>71.052199999999999</v>
+        <v>70.672200000000004</v>
       </c>
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
@@ -8556,29 +8556,29 @@
       </c>
       <c r="J164">
         <f t="shared" ca="1" si="22"/>
-        <v>-0.73</v>
+        <v>-0.85</v>
       </c>
       <c r="K164">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.23</v>
+        <v>-0.87</v>
       </c>
       <c r="L164">
         <v>0.5</v>
       </c>
       <c r="M164">
         <f t="shared" ca="1" si="17"/>
-        <v>-2.847800000000003</v>
+        <v>-3.2278000000000024</v>
       </c>
       <c r="N164">
         <f t="shared" ca="1" si="18"/>
-        <v>-3.8535859269282935</v>
+        <v>-4.3677943166441136</v>
       </c>
       <c r="O164">
         <f t="shared" ca="1" si="19"/>
-        <v>8.1099648400000177</v>
-      </c>
-    </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+        <v>10.418692840000016</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>163</v>
       </c>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="D165" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>60.220300000000002</v>
+        <v>60.1203</v>
       </c>
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
@@ -8605,29 +8605,29 @@
       </c>
       <c r="J165">
         <f t="shared" ca="1" si="22"/>
-        <v>-0.71</v>
+        <v>-0.48</v>
       </c>
       <c r="K165">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.4</v>
+        <v>-0.83</v>
       </c>
       <c r="L165">
         <v>0.5</v>
       </c>
       <c r="M165">
         <f t="shared" ca="1" si="17"/>
-        <v>2.6202999999999999</v>
+        <v>2.5202999999999998</v>
       </c>
       <c r="N165">
         <f t="shared" ca="1" si="18"/>
-        <v>4.54913194444444</v>
+        <v>4.375520833333324</v>
       </c>
       <c r="O165">
         <f t="shared" ca="1" si="19"/>
-        <v>6.8659720899999996</v>
-      </c>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+        <v>6.351912089999999</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>164</v>
       </c>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="D166" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>59.925799999999995</v>
+        <v>59.330799999999996</v>
       </c>
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
@@ -8654,29 +8654,29 @@
       </c>
       <c r="J166">
         <f t="shared" ca="1" si="22"/>
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="K166">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.11</v>
+        <v>-0.41</v>
       </c>
       <c r="L166">
         <v>0.5</v>
       </c>
       <c r="M166">
         <f t="shared" ca="1" si="17"/>
-        <v>2.0257999999999994</v>
+        <v>1.4307999999999996</v>
       </c>
       <c r="N166">
         <f t="shared" ca="1" si="18"/>
-        <v>3.4987910189982596</v>
+        <v>2.4711571675302135</v>
       </c>
       <c r="O166">
         <f t="shared" ca="1" si="19"/>
-        <v>4.1038656399999978</v>
-      </c>
-    </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2.047188639999999</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>165</v>
       </c>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="D167" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>24.95365</v>
+        <v>24.94605</v>
       </c>
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
@@ -8703,29 +8703,29 @@
       </c>
       <c r="J167">
         <f t="shared" ca="1" si="22"/>
-        <v>7.7999999999999996E-3</v>
+        <v>-9.4999999999999998E-3</v>
       </c>
       <c r="K167">
         <f t="shared" ca="1" si="23"/>
-        <v>-5.8999999999999999E-3</v>
+        <v>-3.8E-3</v>
       </c>
       <c r="L167">
         <v>0.5</v>
       </c>
       <c r="M167">
         <f t="shared" ca="1" si="17"/>
-        <v>2.3536499999999987</v>
+        <v>2.3460499999999986</v>
       </c>
       <c r="N167">
         <f t="shared" ca="1" si="18"/>
-        <v>10.414380530973432</v>
+        <v>10.380752212389366</v>
       </c>
       <c r="O167">
         <f t="shared" ca="1" si="19"/>
-        <v>5.5396683224999936</v>
-      </c>
-    </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+        <v>5.5039506024999936</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>166</v>
       </c>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="D168" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>26.01135</v>
+        <v>26.006900000000002</v>
       </c>
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
@@ -8752,29 +8752,29 @@
       </c>
       <c r="J168">
         <f t="shared" ca="1" si="22"/>
-        <v>-1.8E-3</v>
+        <v>6.7999999999999996E-3</v>
       </c>
       <c r="K168">
         <f t="shared" ca="1" si="23"/>
-        <v>7.4999999999999997E-3</v>
+        <v>-0.01</v>
       </c>
       <c r="L168">
         <v>0.5</v>
       </c>
       <c r="M168">
         <f t="shared" ca="1" si="17"/>
-        <v>2.6113500000000012</v>
+        <v>2.6069000000000013</v>
       </c>
       <c r="N168">
         <f t="shared" ca="1" si="18"/>
-        <v>11.159615384615385</v>
+        <v>11.140598290598302</v>
       </c>
       <c r="O168">
         <f t="shared" ca="1" si="19"/>
-        <v>6.8191488225000061</v>
-      </c>
-    </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+        <v>6.7959276100000068</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>167</v>
       </c>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="D169" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>23.396699999999999</v>
+        <v>23.397500000000001</v>
       </c>
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
@@ -8801,29 +8801,29 @@
       </c>
       <c r="J169">
         <f t="shared" ca="1" si="22"/>
-        <v>7.7000000000000002E-3</v>
+        <v>8.6E-3</v>
       </c>
       <c r="K169">
         <f t="shared" ca="1" si="23"/>
-        <v>8.2000000000000007E-3</v>
+        <v>8.8999999999999999E-3</v>
       </c>
       <c r="L169">
         <v>0.5</v>
       </c>
       <c r="M169">
         <f t="shared" ca="1" si="17"/>
-        <v>-1.0133000000000003</v>
+        <v>-1.0125000000000002</v>
       </c>
       <c r="N169">
         <f t="shared" ca="1" si="18"/>
-        <v>-4.1511675542810327</v>
+        <v>-4.1478902089307601</v>
       </c>
       <c r="O169">
         <f t="shared" ca="1" si="19"/>
-        <v>1.0267768900000007</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.0251562500000004</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>168</v>
       </c>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="D170" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>44.884499999999996</v>
+        <v>44.6145</v>
       </c>
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
@@ -8850,29 +8850,29 @@
       </c>
       <c r="J170">
         <f t="shared" ca="1" si="22"/>
-        <v>0.59</v>
+        <v>-0.44</v>
       </c>
       <c r="K170">
         <f t="shared" ca="1" si="23"/>
-        <v>0.19</v>
+        <v>0.68</v>
       </c>
       <c r="L170">
         <v>0.5</v>
       </c>
       <c r="M170">
         <f t="shared" ca="1" si="17"/>
-        <v>2.3045000000000004</v>
+        <v>2.0345000000000004</v>
       </c>
       <c r="N170">
         <f t="shared" ca="1" si="18"/>
-        <v>5.4121653358384147</v>
+        <v>4.7780648191639408</v>
       </c>
       <c r="O170">
         <f t="shared" ca="1" si="19"/>
-        <v>5.3107202500000019</v>
-      </c>
-    </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4.1391902500000013</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>169</v>
       </c>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="D171" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>23.5413</v>
+        <v>23.555399999999999</v>
       </c>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
@@ -8899,29 +8899,29 @@
       </c>
       <c r="J171">
         <f t="shared" ca="1" si="22"/>
-        <v>-9.2999999999999992E-3</v>
+        <v>-1E-4</v>
       </c>
       <c r="K171">
         <f t="shared" ca="1" si="23"/>
-        <v>-9.1999999999999998E-3</v>
+        <v>9.7999999999999997E-3</v>
       </c>
       <c r="L171">
         <v>0.5</v>
       </c>
       <c r="M171">
         <f t="shared" ca="1" si="17"/>
-        <v>0.15129999999999888</v>
+        <v>0.16539999999999885</v>
       </c>
       <c r="N171">
         <f t="shared" ca="1" si="18"/>
-        <v>0.64685763146643538</v>
+        <v>0.70713980333474424</v>
       </c>
       <c r="O171">
         <f t="shared" ca="1" si="19"/>
-        <v>2.2891689999999663E-2</v>
-      </c>
-    </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2.735715999999962E-2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>170</v>
       </c>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="D172" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>85.960000000000008</v>
+        <v>85.73</v>
       </c>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
@@ -8948,29 +8948,29 @@
       </c>
       <c r="J172">
         <f t="shared" ca="1" si="22"/>
-        <v>0.15</v>
+        <v>-0.2</v>
       </c>
       <c r="K172">
         <f t="shared" ca="1" si="23"/>
-        <v>0.04</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="L172">
         <v>0.5</v>
       </c>
       <c r="M172">
         <f t="shared" ca="1" si="17"/>
-        <v>0.11999999999999858</v>
+        <v>-0.11000000000000143</v>
       </c>
       <c r="N172">
         <f t="shared" ca="1" si="18"/>
-        <v>0.13979496738119046</v>
+        <v>-0.12814538676607645</v>
       </c>
       <c r="O172">
         <f t="shared" ca="1" si="19"/>
-        <v>1.439999999999966E-2</v>
-      </c>
-    </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.2100000000000315E-2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>171</v>
       </c>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="D173" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>26.115500000000001</v>
+        <v>26.129349999999999</v>
       </c>
       <c r="E173" s="1"/>
       <c r="F173" s="1"/>
@@ -8997,29 +8997,29 @@
       </c>
       <c r="J173">
         <f t="shared" ca="1" si="22"/>
-        <v>-5.8999999999999999E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="K173">
         <f t="shared" ca="1" si="23"/>
-        <v>-8.5000000000000006E-3</v>
+        <v>8.8999999999999999E-3</v>
       </c>
       <c r="L173">
         <v>0.5</v>
       </c>
       <c r="M173">
         <f t="shared" ca="1" si="17"/>
-        <v>0.83549999999999891</v>
+        <v>0.84934999999999883</v>
       </c>
       <c r="N173">
         <f t="shared" ca="1" si="18"/>
-        <v>3.3049841772151867</v>
+        <v>3.3597705696202462</v>
       </c>
       <c r="O173">
         <f t="shared" ca="1" si="19"/>
-        <v>0.69806024999999816</v>
-      </c>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.721395422499998</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>172</v>
       </c>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D174" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>85.905850000000001</v>
+        <v>86.445849999999993</v>
       </c>
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
@@ -9046,29 +9046,29 @@
       </c>
       <c r="J174">
         <f t="shared" ca="1" si="22"/>
-        <v>-0.04</v>
+        <v>0.74</v>
       </c>
       <c r="K174">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.63</v>
+        <v>-0.33</v>
       </c>
       <c r="L174">
         <v>0.5</v>
       </c>
       <c r="M174">
         <f t="shared" ca="1" si="17"/>
-        <v>-1.4741500000000007</v>
+        <v>-0.93415000000000081</v>
       </c>
       <c r="N174">
         <f t="shared" ca="1" si="18"/>
-        <v>-1.6870565346761235</v>
+        <v>-1.0690661478599206</v>
       </c>
       <c r="O174">
         <f t="shared" ca="1" si="19"/>
-        <v>2.1731182225000021</v>
-      </c>
-    </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.8726362225000015</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>173</v>
       </c>
@@ -9080,7 +9080,7 @@
       </c>
       <c r="D175" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>21.950749999999999</v>
+        <v>21.945900000000002</v>
       </c>
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
@@ -9095,29 +9095,29 @@
       </c>
       <c r="J175">
         <f t="shared" ca="1" si="22"/>
-        <v>8.9999999999999998E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="K175">
         <f t="shared" ca="1" si="23"/>
-        <v>1.2999999999999999E-3</v>
+        <v>-7.7000000000000002E-3</v>
       </c>
       <c r="L175">
         <v>0.5</v>
       </c>
       <c r="M175">
         <f t="shared" ca="1" si="17"/>
-        <v>1.8907500000000015</v>
+        <v>1.8859000000000015</v>
       </c>
       <c r="N175">
         <f t="shared" ca="1" si="18"/>
-        <v>9.4254735792622224</v>
+        <v>9.401296111665026</v>
       </c>
       <c r="O175">
         <f t="shared" ca="1" si="19"/>
-        <v>3.5749355625000057</v>
-      </c>
-    </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+        <v>3.5566188100000056</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>174</v>
       </c>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="D176" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>52.216549999999998</v>
+        <v>50.656550000000003</v>
       </c>
       <c r="E176" s="1"/>
       <c r="F176" s="1"/>
@@ -9144,29 +9144,29 @@
       </c>
       <c r="J176">
         <f t="shared" ca="1" si="22"/>
-        <v>0.76</v>
+        <v>-0.97</v>
       </c>
       <c r="K176">
         <f t="shared" ca="1" si="23"/>
-        <v>0.83</v>
+        <v>-0.56000000000000005</v>
       </c>
       <c r="L176">
         <v>0.5</v>
       </c>
       <c r="M176">
         <f t="shared" ca="1" si="17"/>
-        <v>-0.27345000000000214</v>
+        <v>-1.833450000000002</v>
       </c>
       <c r="N176">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.52095637264241157</v>
+        <v>-3.4929510382930018</v>
       </c>
       <c r="O176">
         <f t="shared" ca="1" si="19"/>
-        <v>7.477490250000117E-2</v>
-      </c>
-    </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+        <v>3.3615389025000075</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>175</v>
       </c>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="D177" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>26.009050000000002</v>
+        <v>26.0213</v>
       </c>
       <c r="E177" s="1"/>
       <c r="F177" s="1"/>
@@ -9193,29 +9193,29 @@
       </c>
       <c r="J177">
         <f t="shared" ca="1" si="22"/>
-        <v>-8.8000000000000005E-3</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="K177">
         <f t="shared" ca="1" si="23"/>
-        <v>-5.0000000000000001E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="L177">
         <v>0.5</v>
       </c>
       <c r="M177">
         <f t="shared" ca="1" si="17"/>
-        <v>0.60905000000000165</v>
+        <v>0.62130000000000163</v>
       </c>
       <c r="N177">
         <f t="shared" ca="1" si="18"/>
-        <v>2.3978346456692945</v>
+        <v>2.4460629921259969</v>
       </c>
       <c r="O177">
         <f t="shared" ca="1" si="19"/>
-        <v>0.37094190250000203</v>
-      </c>
-    </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.38601369000000202</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>176</v>
       </c>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="D178" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>86.288899999999998</v>
+        <v>85.553899999999999</v>
       </c>
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
@@ -9242,29 +9242,29 @@
       </c>
       <c r="J178">
         <f t="shared" ca="1" si="22"/>
-        <v>0.8</v>
+        <v>-0.81</v>
       </c>
       <c r="K178">
         <f t="shared" ca="1" si="23"/>
-        <v>0.39</v>
+        <v>0.53</v>
       </c>
       <c r="L178">
         <v>0.5</v>
       </c>
       <c r="M178">
         <f t="shared" ca="1" si="17"/>
-        <v>1.0888999999999964</v>
+        <v>0.35389999999999644</v>
       </c>
       <c r="N178">
         <f t="shared" ca="1" si="18"/>
-        <v>1.2780516431924793</v>
+        <v>0.41537558685444953</v>
       </c>
       <c r="O178">
         <f t="shared" ca="1" si="19"/>
-        <v>1.1857032099999922</v>
-      </c>
-    </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.12524520999999747</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>177</v>
       </c>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="D179" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>49.157350000000001</v>
+        <v>48.292349999999999</v>
       </c>
       <c r="E179" s="1"/>
       <c r="F179" s="1"/>
@@ -9291,29 +9291,29 @@
       </c>
       <c r="J179">
         <f t="shared" ca="1" si="22"/>
-        <v>0.77</v>
+        <v>-0.68</v>
       </c>
       <c r="K179">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.52</v>
+        <v>-0.8</v>
       </c>
       <c r="L179">
         <v>0.5</v>
       </c>
       <c r="M179">
         <f t="shared" ca="1" si="17"/>
-        <v>6.0573499999999996</v>
+        <v>5.1923499999999994</v>
       </c>
       <c r="N179">
         <f t="shared" ca="1" si="18"/>
-        <v>14.054176334106728</v>
+        <v>12.047215777262178</v>
       </c>
       <c r="O179">
         <f t="shared" ca="1" si="19"/>
-        <v>36.691489022499994</v>
-      </c>
-    </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+        <v>26.960498522499993</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>178</v>
       </c>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="D180" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>40.439500000000002</v>
+        <v>40.554499999999997</v>
       </c>
       <c r="E180" s="1"/>
       <c r="F180" s="1"/>
@@ -9340,29 +9340,29 @@
       </c>
       <c r="J180">
         <f t="shared" ca="1" si="22"/>
-        <v>-0.6</v>
+        <v>0.15</v>
       </c>
       <c r="K180">
         <f t="shared" ca="1" si="23"/>
-        <v>0.14000000000000001</v>
+        <v>-0.38</v>
       </c>
       <c r="L180">
         <v>0.5</v>
       </c>
       <c r="M180">
         <f t="shared" ca="1" si="17"/>
-        <v>-0.56050000000000066</v>
+        <v>-0.44550000000000067</v>
       </c>
       <c r="N180">
         <f t="shared" ca="1" si="18"/>
-        <v>-1.367073170731703</v>
+        <v>-1.0865853658536651</v>
       </c>
       <c r="O180">
         <f t="shared" ca="1" si="19"/>
-        <v>0.31416025000000075</v>
-      </c>
-    </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.1984702500000006</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>179</v>
       </c>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="D181" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>9.3766999999999996</v>
+        <v>9.3763500000000004</v>
       </c>
       <c r="E181" s="1"/>
       <c r="F181" s="1"/>
@@ -9389,29 +9389,29 @@
       </c>
       <c r="J181">
         <f t="shared" ca="1" si="22"/>
-        <v>1.1999999999999999E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="K181">
         <f t="shared" ca="1" si="23"/>
-        <v>2.3E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="L181">
         <v>0.5</v>
       </c>
       <c r="M181">
         <f t="shared" ca="1" si="17"/>
-        <v>1.3767</v>
+        <v>1.37635</v>
       </c>
       <c r="N181">
         <f t="shared" ca="1" si="18"/>
-        <v>17.208749999999995</v>
+        <v>17.204375000000006</v>
       </c>
       <c r="O181">
         <f t="shared" ca="1" si="19"/>
-        <v>1.8953028900000002</v>
-      </c>
-    </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.8943393224999998</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>180</v>
       </c>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="D182" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>56.82235</v>
+        <v>57.552349999999997</v>
       </c>
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
@@ -9438,29 +9438,29 @@
       </c>
       <c r="J182">
         <f t="shared" ca="1" si="22"/>
-        <v>0.01</v>
+        <v>0.31</v>
       </c>
       <c r="K182">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.17</v>
+        <v>0.99</v>
       </c>
       <c r="L182">
         <v>0.5</v>
       </c>
       <c r="M182">
         <f t="shared" ca="1" si="17"/>
-        <v>-4.1776500000000016</v>
+        <v>-3.4476500000000017</v>
       </c>
       <c r="N182">
         <f t="shared" ca="1" si="18"/>
-        <v>-6.848606557377046</v>
+        <v>-5.651885245901644</v>
       </c>
       <c r="O182">
         <f t="shared" ca="1" si="19"/>
-        <v>17.452759522500013</v>
-      </c>
-    </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+        <v>11.886290522500012</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>181</v>
       </c>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="D183" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>15.9148</v>
+        <v>15.922799999999999</v>
       </c>
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
@@ -9487,29 +9487,29 @@
       </c>
       <c r="J183">
         <f t="shared" ca="1" si="22"/>
-        <v>5.8999999999999999E-3</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="K183">
         <f t="shared" ca="1" si="23"/>
-        <v>-7.4000000000000003E-3</v>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="L183">
         <v>0.5</v>
       </c>
       <c r="M183">
         <f t="shared" ca="1" si="17"/>
-        <v>-5.0852000000000004</v>
+        <v>-5.0772000000000004</v>
       </c>
       <c r="N183">
         <f t="shared" ca="1" si="18"/>
-        <v>-24.215238095238099</v>
+        <v>-24.177142857142865</v>
       </c>
       <c r="O183">
         <f t="shared" ca="1" si="19"/>
-        <v>25.859259040000005</v>
-      </c>
-    </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+        <v>25.777959840000005</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>182</v>
       </c>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="D184" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>31.233599999999999</v>
+        <v>31.237300000000001</v>
       </c>
       <c r="E184" s="1"/>
       <c r="F184" s="1"/>
@@ -9536,29 +9536,29 @@
       </c>
       <c r="J184">
         <f t="shared" ca="1" si="22"/>
-        <v>5.1999999999999998E-3</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="K184">
         <f t="shared" ca="1" si="23"/>
-        <v>-6.0000000000000001E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="L184">
         <v>0.5</v>
       </c>
       <c r="M184">
         <f t="shared" ca="1" si="17"/>
-        <v>2.0336000000000007</v>
+        <v>2.0373000000000006</v>
       </c>
       <c r="N184">
         <f t="shared" ca="1" si="18"/>
-        <v>6.9643835616438388</v>
+        <v>6.9770547945205541</v>
       </c>
       <c r="O184">
         <f t="shared" ca="1" si="19"/>
-        <v>4.1355289600000029</v>
-      </c>
-    </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4.1505912900000022</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>183</v>
       </c>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="D185" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>45.360199999999999</v>
+        <v>45.160199999999996</v>
       </c>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
@@ -9585,29 +9585,29 @@
       </c>
       <c r="J185">
         <f t="shared" ca="1" si="22"/>
-        <v>0.65</v>
+        <v>0.43</v>
       </c>
       <c r="K185">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.11</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="L185">
         <v>0.5</v>
       </c>
       <c r="M185">
         <f t="shared" ca="1" si="17"/>
-        <v>1.0602000000000023</v>
+        <v>0.8602000000000023</v>
       </c>
       <c r="N185">
         <f t="shared" ca="1" si="18"/>
-        <v>2.3932279909706589</v>
+        <v>1.9417607223476185</v>
       </c>
       <c r="O185">
         <f t="shared" ca="1" si="19"/>
-        <v>1.1240240400000048</v>
-      </c>
-    </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.73994404000000391</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>184</v>
       </c>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="D186" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>46.103500000000004</v>
+        <v>46.158500000000004</v>
       </c>
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
@@ -9634,29 +9634,29 @@
       </c>
       <c r="J186">
         <f t="shared" ca="1" si="22"/>
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="K186">
         <f t="shared" ca="1" si="23"/>
-        <v>0.28999999999999998</v>
+        <v>0.22</v>
       </c>
       <c r="L186">
         <v>0.5</v>
       </c>
       <c r="M186">
         <f t="shared" ca="1" si="17"/>
-        <v>-0.99650000000000061</v>
+        <v>-0.94150000000000056</v>
       </c>
       <c r="N186">
         <f t="shared" ca="1" si="18"/>
-        <v>-2.1157112526539179</v>
+        <v>-1.9989384288747303</v>
       </c>
       <c r="O186">
         <f t="shared" ca="1" si="19"/>
-        <v>0.99301225000000126</v>
-      </c>
-    </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.88642225000000108</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>185</v>
       </c>
@@ -9668,7 +9668,7 @@
       </c>
       <c r="D187" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>88.914599999999993</v>
+        <v>88.909599999999998</v>
       </c>
       <c r="E187" s="1"/>
       <c r="F187" s="1"/>
@@ -9683,29 +9683,29 @@
       </c>
       <c r="J187">
         <f t="shared" ca="1" si="22"/>
-        <v>-0.47</v>
+        <v>0.09</v>
       </c>
       <c r="K187">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.18</v>
+        <v>-0.75</v>
       </c>
       <c r="L187">
         <v>0.5</v>
       </c>
       <c r="M187">
         <f t="shared" ca="1" si="17"/>
-        <v>-0.68539999999999845</v>
+        <v>-0.69039999999999857</v>
       </c>
       <c r="N187">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.76495535714286023</v>
+        <v>-0.77053571428571388</v>
       </c>
       <c r="O187">
         <f t="shared" ca="1" si="19"/>
-        <v>0.46977315999999786</v>
-      </c>
-    </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.47665215999999805</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>186</v>
       </c>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="D188" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>69.180000000000007</v>
+        <v>69.715000000000003</v>
       </c>
       <c r="E188" s="1"/>
       <c r="F188" s="1"/>
@@ -9732,29 +9732,29 @@
       </c>
       <c r="J188">
         <f t="shared" ca="1" si="22"/>
-        <v>-0.89</v>
+        <v>0.74</v>
       </c>
       <c r="K188">
         <f t="shared" ca="1" si="23"/>
-        <v>0.94</v>
+        <v>0.38</v>
       </c>
       <c r="L188">
         <v>0.5</v>
       </c>
       <c r="M188">
         <f t="shared" ca="1" si="17"/>
-        <v>0.27999999999999542</v>
+        <v>0.81499999999999551</v>
       </c>
       <c r="N188">
         <f t="shared" ca="1" si="18"/>
-        <v>0.40638606676342004</v>
+        <v>1.1828737300435321</v>
       </c>
       <c r="O188">
         <f t="shared" ca="1" si="19"/>
-        <v>7.839999999999743E-2</v>
-      </c>
-    </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.66422499999999263</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>187</v>
       </c>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="D189" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>61.682650000000002</v>
+        <v>62.032649999999997</v>
       </c>
       <c r="E189" s="1"/>
       <c r="F189" s="1"/>
@@ -9781,29 +9781,29 @@
       </c>
       <c r="J189">
         <f t="shared" ca="1" si="22"/>
-        <v>-1</v>
+        <v>-0.64</v>
       </c>
       <c r="K189">
         <f t="shared" ca="1" si="23"/>
-        <v>0.15</v>
+        <v>0.49</v>
       </c>
       <c r="L189">
         <v>0.5</v>
       </c>
       <c r="M189">
         <f t="shared" ca="1" si="17"/>
-        <v>-4.3173500000000002</v>
+        <v>-3.9673500000000006</v>
       </c>
       <c r="N189">
         <f t="shared" ca="1" si="18"/>
-        <v>-6.5414393939393856</v>
+        <v>-6.0111363636363713</v>
       </c>
       <c r="O189">
         <f t="shared" ca="1" si="19"/>
-        <v>18.639511022500002</v>
-      </c>
-    </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+        <v>15.739866022500005</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>188</v>
       </c>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="D190" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>65.934250000000006</v>
+        <v>65.809250000000006</v>
       </c>
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
@@ -9830,29 +9830,29 @@
       </c>
       <c r="J190">
         <f t="shared" ca="1" si="22"/>
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="K190">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.2</v>
+        <v>-0.46</v>
       </c>
       <c r="L190">
         <v>0.5</v>
       </c>
       <c r="M190">
         <f t="shared" ca="1" si="17"/>
-        <v>-2.5657500000000004</v>
+        <v>-2.6907500000000004</v>
       </c>
       <c r="N190">
         <f t="shared" ca="1" si="18"/>
-        <v>-3.7456204379561986</v>
+        <v>-3.9281021897810131</v>
       </c>
       <c r="O190">
         <f t="shared" ca="1" si="19"/>
-        <v>6.5830730625000022</v>
-      </c>
-    </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+        <v>7.2401355625000026</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>189</v>
       </c>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="D191" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>35.126600000000003</v>
+        <v>33.551600000000001</v>
       </c>
       <c r="E191" s="1"/>
       <c r="F191" s="1"/>
@@ -9879,29 +9879,29 @@
       </c>
       <c r="J191">
         <f t="shared" ca="1" si="22"/>
-        <v>0.88</v>
+        <v>-0.66</v>
       </c>
       <c r="K191">
         <f t="shared" ca="1" si="23"/>
-        <v>0.91</v>
+        <v>-0.7</v>
       </c>
       <c r="L191">
         <v>0.5</v>
       </c>
       <c r="M191">
         <f t="shared" ca="1" si="17"/>
-        <v>1.0265999999999988</v>
+        <v>-0.54840000000000111</v>
       </c>
       <c r="N191">
         <f t="shared" ca="1" si="18"/>
-        <v>3.0105571847507395</v>
+        <v>-1.6082111436950153</v>
       </c>
       <c r="O191">
         <f t="shared" ca="1" si="19"/>
-        <v>1.0539075599999976</v>
-      </c>
-    </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.30074256000000121</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>190</v>
       </c>
@@ -9913,7 +9913,7 @@
       </c>
       <c r="D192" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>35.591000000000001</v>
+        <v>35.206000000000003</v>
       </c>
       <c r="E192" s="1"/>
       <c r="F192" s="1"/>
@@ -9928,29 +9928,29 @@
       </c>
       <c r="J192">
         <f t="shared" ca="1" si="22"/>
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="K192">
         <f t="shared" ca="1" si="23"/>
-        <v>0.79</v>
+        <v>-0.08</v>
       </c>
       <c r="L192">
         <v>0.5</v>
       </c>
       <c r="M192">
         <f t="shared" ca="1" si="17"/>
-        <v>-9.0000000000007296E-3</v>
+        <v>-0.39400000000000074</v>
       </c>
       <c r="N192">
         <f t="shared" ca="1" si="18"/>
-        <v>-2.5280898876400837E-2</v>
+        <v>-1.1067415730336982</v>
       </c>
       <c r="O192">
         <f t="shared" ca="1" si="19"/>
-        <v>8.1000000000013136E-5</v>
-      </c>
-    </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.1552360000000006</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>191</v>
       </c>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="D193" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>18.811199999999999</v>
+        <v>18.80705</v>
       </c>
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
@@ -9977,29 +9977,29 @@
       </c>
       <c r="J193">
         <f t="shared" ca="1" si="22"/>
-        <v>3.3999999999999998E-3</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="K193">
         <f t="shared" ca="1" si="23"/>
-        <v>-1.1999999999999999E-3</v>
+        <v>-8.5000000000000006E-3</v>
       </c>
       <c r="L193">
         <v>0.5</v>
       </c>
       <c r="M193">
         <f t="shared" ca="1" si="17"/>
-        <v>2.0111999999999997</v>
+        <v>2.0070499999999996</v>
       </c>
       <c r="N193">
         <f t="shared" ca="1" si="18"/>
-        <v>11.971428571428566</v>
+        <v>11.946726190476188</v>
       </c>
       <c r="O193">
         <f t="shared" ca="1" si="19"/>
-        <v>4.0449254399999983</v>
-      </c>
-    </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4.0282497024999984</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>192</v>
       </c>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="D194" s="4">
         <f t="shared" ca="1" si="16"/>
-        <v>27.858350000000002</v>
+        <v>27.861050000000002</v>
       </c>
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
@@ -10026,29 +10026,29 @@
       </c>
       <c r="J194">
         <f t="shared" ca="1" si="22"/>
-        <v>6.0000000000000001E-3</v>
+        <v>7.4000000000000003E-3</v>
       </c>
       <c r="K194">
         <f t="shared" ca="1" si="23"/>
-        <v>0</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="L194">
         <v>0.5</v>
       </c>
       <c r="M194">
         <f t="shared" ca="1" si="17"/>
-        <v>1.2583499999999999</v>
+        <v>1.26105</v>
       </c>
       <c r="N194">
         <f t="shared" ca="1" si="18"/>
-        <v>4.7306390977443602</v>
+        <v>4.7407894736842149</v>
       </c>
       <c r="O194">
         <f t="shared" ca="1" si="19"/>
-        <v>1.5834447224999997</v>
-      </c>
-    </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.5902471025</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>193</v>
       </c>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D195" s="4">
         <f t="shared" ref="D195:D209" ca="1" si="24">B195+M195</f>
-        <v>37.094249999999995</v>
+        <v>38.009249999999994</v>
       </c>
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
@@ -10075,29 +10075,29 @@
       </c>
       <c r="J195">
         <f t="shared" ca="1" si="22"/>
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
       <c r="K195">
         <f t="shared" ca="1" si="23"/>
-        <v>-0.81</v>
+        <v>0.32</v>
       </c>
       <c r="L195">
         <v>0.5</v>
       </c>
       <c r="M195">
         <f t="shared" ref="M195:M209" ca="1" si="25">(I195+J195+K195)*L195</f>
-        <v>-4.2057499999999992</v>
+        <v>-3.2907499999999992</v>
       </c>
       <c r="N195">
         <f t="shared" ref="N195:N209" ca="1" si="26">((D195/B195)-1)*100</f>
-        <v>-10.183414043583539</v>
+        <v>-7.9679176755448005</v>
       </c>
       <c r="O195">
         <f t="shared" ref="O195:O209" ca="1" si="27">M195^2</f>
-        <v>17.688333062499993</v>
-      </c>
-    </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+        <v>10.829035562499994</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>194</v>
       </c>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D196" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>56.659849999999999</v>
+        <v>57.124850000000002</v>
       </c>
       <c r="E196" s="1"/>
       <c r="F196" s="1"/>
@@ -10124,29 +10124,29 @@
       </c>
       <c r="J196">
         <f t="shared" ref="J196:J209" ca="1" si="30">IF(B196 &lt; 30, RANDBETWEEN(-100, 100) / 10000, RANDBETWEEN(-100,100) / 100)</f>
-        <v>-0.66</v>
+        <v>0.81</v>
       </c>
       <c r="K196">
         <f t="shared" ref="K196:K209" ca="1" si="31">IF(B196 &lt; 30, RANDBETWEEN(-100, 100) / 10000, RANDBETWEEN(-100,100) / 100)</f>
-        <v>0.99</v>
+        <v>0.45</v>
       </c>
       <c r="L196">
         <v>0.5</v>
       </c>
       <c r="M196">
         <f t="shared" ca="1" si="25"/>
-        <v>-1.6401499999999976</v>
+        <v>-1.1751499999999975</v>
       </c>
       <c r="N196">
         <f t="shared" ca="1" si="26"/>
-        <v>-2.8132933104631164</v>
+        <v>-2.015694682675806</v>
       </c>
       <c r="O196">
         <f t="shared" ca="1" si="27"/>
-        <v>2.690092022499992</v>
-      </c>
-    </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.3809775224999941</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>195</v>
       </c>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="D197" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>14.12725</v>
+        <v>14.126200000000001</v>
       </c>
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
@@ -10173,29 +10173,29 @@
       </c>
       <c r="J197">
         <f t="shared" ca="1" si="30"/>
-        <v>-3.5999999999999999E-3</v>
+        <v>-9.1999999999999998E-3</v>
       </c>
       <c r="K197">
         <f t="shared" ca="1" si="31"/>
-        <v>5.9999999999999995E-4</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="L197">
         <v>0.5</v>
       </c>
       <c r="M197">
         <f t="shared" ca="1" si="25"/>
-        <v>7.6272500000000001</v>
+        <v>7.6261999999999999</v>
       </c>
       <c r="N197">
         <f t="shared" ca="1" si="26"/>
-        <v>117.34230769230768</v>
+        <v>117.32615384615386</v>
       </c>
       <c r="O197">
         <f t="shared" ca="1" si="27"/>
-        <v>58.1749425625</v>
-      </c>
-    </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+        <v>58.158926439999995</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>196</v>
       </c>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="D198" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>60.594899999999996</v>
+        <v>60.774899999999995</v>
       </c>
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
@@ -10222,29 +10222,29 @@
       </c>
       <c r="J198">
         <f t="shared" ca="1" si="30"/>
-        <v>0.4</v>
+        <v>-0.49</v>
       </c>
       <c r="K198">
         <f t="shared" ca="1" si="31"/>
-        <v>-0.7</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="L198">
         <v>0.5</v>
       </c>
       <c r="M198">
         <f t="shared" ca="1" si="25"/>
-        <v>-1.2050999999999994</v>
+        <v>-1.0250999999999997</v>
       </c>
       <c r="N198">
         <f t="shared" ca="1" si="26"/>
-        <v>-1.9500000000000073</v>
+        <v>-1.6587378640776751</v>
       </c>
       <c r="O198">
         <f t="shared" ca="1" si="27"/>
-        <v>1.4522660099999984</v>
-      </c>
-    </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+        <v>1.0508300099999994</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>197</v>
       </c>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="D199" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>54.799149999999997</v>
+        <v>55.089150000000004</v>
       </c>
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
@@ -10271,29 +10271,29 @@
       </c>
       <c r="J199">
         <f t="shared" ca="1" si="30"/>
-        <v>-0.81</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="K199">
         <f t="shared" ca="1" si="31"/>
-        <v>0.06</v>
+        <v>-0.72</v>
       </c>
       <c r="L199">
         <v>0.5</v>
       </c>
       <c r="M199">
         <f t="shared" ca="1" si="25"/>
-        <v>-0.70084999999999908</v>
+        <v>-0.41084999999999905</v>
       </c>
       <c r="N199">
         <f t="shared" ca="1" si="26"/>
-        <v>-1.2627927927927995</v>
+        <v>-0.74027027027026016</v>
       </c>
       <c r="O199">
         <f t="shared" ca="1" si="27"/>
-        <v>0.49119072249999873</v>
-      </c>
-    </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.16879772249999922</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>198</v>
       </c>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="D200" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>29.546600000000005</v>
+        <v>29.540600000000005</v>
       </c>
       <c r="E200" s="1"/>
       <c r="F200" s="1"/>
@@ -10320,29 +10320,29 @@
       </c>
       <c r="J200">
         <f t="shared" ca="1" si="30"/>
-        <v>3.8999999999999998E-3</v>
+        <v>-5.1999999999999998E-3</v>
       </c>
       <c r="K200">
         <f t="shared" ca="1" si="31"/>
-        <v>-4.7999999999999996E-3</v>
+        <v>-7.7000000000000002E-3</v>
       </c>
       <c r="L200">
         <v>0.5</v>
       </c>
       <c r="M200">
         <f t="shared" ca="1" si="25"/>
-        <v>8.9466000000000019</v>
+        <v>8.9406000000000017</v>
       </c>
       <c r="N200">
         <f t="shared" ca="1" si="26"/>
-        <v>43.430097087378662</v>
+        <v>43.400970873786427</v>
       </c>
       <c r="O200">
         <f t="shared" ca="1" si="27"/>
-        <v>80.041651560000034</v>
-      </c>
-    </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+        <v>79.934328360000023</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>199</v>
       </c>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="D201" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>55.667000000000002</v>
+        <v>55.726999999999997</v>
       </c>
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
@@ -10369,29 +10369,29 @@
       </c>
       <c r="J201">
         <f t="shared" ca="1" si="30"/>
-        <v>-0.54</v>
+        <v>-0.92</v>
       </c>
       <c r="K201">
         <f t="shared" ca="1" si="31"/>
-        <v>-0.56000000000000005</v>
+        <v>-0.06</v>
       </c>
       <c r="L201">
         <v>0.5</v>
       </c>
       <c r="M201">
         <f t="shared" ca="1" si="25"/>
-        <v>-0.83300000000000129</v>
+        <v>-0.77300000000000124</v>
       </c>
       <c r="N201">
         <f t="shared" ca="1" si="26"/>
-        <v>-1.4743362831858398</v>
+        <v>-1.3681415929203578</v>
       </c>
       <c r="O201">
         <f t="shared" ca="1" si="27"/>
-        <v>0.6938890000000022</v>
-      </c>
-    </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.59752900000000186</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>200</v>
       </c>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="D202" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>69.113200000000006</v>
+        <v>69.583200000000005</v>
       </c>
       <c r="E202" s="1"/>
       <c r="F202" s="1"/>
@@ -10418,29 +10418,29 @@
       </c>
       <c r="J202">
         <f t="shared" ca="1" si="30"/>
-        <v>-0.42</v>
+        <v>0.43</v>
       </c>
       <c r="K202">
         <f t="shared" ca="1" si="31"/>
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="L202">
         <v>0.5</v>
       </c>
       <c r="M202">
         <f t="shared" ca="1" si="25"/>
-        <v>1.7131999999999952</v>
+        <v>2.1831999999999954</v>
       </c>
       <c r="N202">
         <f t="shared" ca="1" si="26"/>
-        <v>2.5418397626112865</v>
+        <v>3.2391691394658695</v>
       </c>
       <c r="O202">
         <f t="shared" ca="1" si="27"/>
-        <v>2.9350542399999835</v>
-      </c>
-    </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4.7663622399999799</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>201</v>
       </c>
@@ -10452,7 +10452,7 @@
       </c>
       <c r="D203" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>51.514699999999998</v>
+        <v>52.544699999999999</v>
       </c>
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
@@ -10467,29 +10467,29 @@
       </c>
       <c r="J203">
         <f t="shared" ca="1" si="30"/>
-        <v>-0.91</v>
+        <v>-0.09</v>
       </c>
       <c r="K203">
         <f t="shared" ca="1" si="31"/>
-        <v>-0.43</v>
+        <v>0.81</v>
       </c>
       <c r="L203">
         <v>0.5</v>
       </c>
       <c r="M203">
         <f t="shared" ca="1" si="25"/>
-        <v>2.5146999999999995</v>
+        <v>3.5446999999999997</v>
       </c>
       <c r="N203">
         <f t="shared" ca="1" si="26"/>
-        <v>5.1320408163265219</v>
+        <v>7.2340816326530666</v>
       </c>
       <c r="O203">
         <f t="shared" ca="1" si="27"/>
-        <v>6.3237160899999978</v>
-      </c>
-    </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+        <v>12.564898089999998</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>202</v>
       </c>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="D204" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>21.7423</v>
+        <v>21.7501</v>
       </c>
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
@@ -10516,29 +10516,29 @@
       </c>
       <c r="J204">
         <f t="shared" ca="1" si="30"/>
-        <v>-1.1000000000000001E-3</v>
+        <v>5.1999999999999998E-3</v>
       </c>
       <c r="K204">
         <f t="shared" ca="1" si="31"/>
-        <v>-8.8000000000000005E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="L204">
         <v>0.5</v>
       </c>
       <c r="M204">
         <f t="shared" ca="1" si="25"/>
-        <v>0.74229999999999929</v>
+        <v>0.75009999999999932</v>
       </c>
       <c r="N204">
         <f t="shared" ca="1" si="26"/>
-        <v>3.5347619047618961</v>
+        <v>3.571904761904765</v>
       </c>
       <c r="O204">
         <f t="shared" ca="1" si="27"/>
-        <v>0.55100928999999899</v>
-      </c>
-    </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.56265000999999903</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>203</v>
       </c>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="D205" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>25.147949999999998</v>
+        <v>25.146249999999998</v>
       </c>
       <c r="E205" s="1"/>
       <c r="F205" s="1"/>
@@ -10565,29 +10565,29 @@
       </c>
       <c r="J205">
         <f t="shared" ca="1" si="30"/>
-        <v>-8.2000000000000007E-3</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="K205">
         <f t="shared" ca="1" si="31"/>
-        <v>7.9000000000000008E-3</v>
+        <v>-9.1000000000000004E-3</v>
       </c>
       <c r="L205">
         <v>0.5</v>
       </c>
       <c r="M205">
         <f t="shared" ca="1" si="25"/>
-        <v>1.7479500000000008</v>
+        <v>1.7462500000000007</v>
       </c>
       <c r="N205">
         <f t="shared" ca="1" si="26"/>
-        <v>7.4698717948717963</v>
+        <v>7.4626068376068444</v>
       </c>
       <c r="O205">
         <f t="shared" ca="1" si="27"/>
-        <v>3.0553292025000029</v>
-      </c>
-    </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+        <v>3.0493890625000026</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>204</v>
       </c>
@@ -10599,7 +10599,7 @@
       </c>
       <c r="D206" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>46.573250000000002</v>
+        <v>45.97325</v>
       </c>
       <c r="E206" s="1"/>
       <c r="F206" s="1"/>
@@ -10618,25 +10618,25 @@
       </c>
       <c r="K206">
         <f t="shared" ca="1" si="31"/>
-        <v>0.31</v>
+        <v>-0.89</v>
       </c>
       <c r="L206">
         <v>0.5</v>
       </c>
       <c r="M206">
         <f t="shared" ca="1" si="25"/>
-        <v>1.3432500000000023</v>
+        <v>0.74325000000000219</v>
       </c>
       <c r="N206">
         <f t="shared" ca="1" si="26"/>
-        <v>2.969820915321697</v>
+        <v>1.6432677426486908</v>
       </c>
       <c r="O206">
         <f t="shared" ca="1" si="27"/>
-        <v>1.8043205625000061</v>
-      </c>
-    </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.55242056250000326</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>205</v>
       </c>
@@ -10648,7 +10648,7 @@
       </c>
       <c r="D207" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>46.720950000000002</v>
+        <v>46.850949999999997</v>
       </c>
       <c r="E207" s="1"/>
       <c r="F207" s="1"/>
@@ -10663,29 +10663,29 @@
       </c>
       <c r="J207">
         <f t="shared" ca="1" si="30"/>
-        <v>0.46</v>
+        <v>-0.59</v>
       </c>
       <c r="K207">
         <f t="shared" ca="1" si="31"/>
-        <v>-0.96</v>
+        <v>0.35</v>
       </c>
       <c r="L207">
         <v>0.5</v>
       </c>
       <c r="M207">
         <f t="shared" ca="1" si="25"/>
-        <v>-2.2790500000000016</v>
+        <v>-2.1490500000000017</v>
       </c>
       <c r="N207">
         <f t="shared" ca="1" si="26"/>
-        <v>-4.6511224489795833</v>
+        <v>-4.3858163265306231</v>
       </c>
       <c r="O207">
         <f t="shared" ca="1" si="27"/>
-        <v>5.1940689025000069</v>
-      </c>
-    </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4.6184159025000069</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>206</v>
       </c>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="D208" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>44.804300000000005</v>
+        <v>44.944299999999998</v>
       </c>
       <c r="E208" s="1"/>
       <c r="F208" s="1"/>
@@ -10712,29 +10712,29 @@
       </c>
       <c r="J208">
         <f t="shared" ca="1" si="30"/>
-        <v>0.18</v>
+        <v>0.95</v>
       </c>
       <c r="K208">
         <f t="shared" ca="1" si="31"/>
-        <v>-0.32</v>
+        <v>-0.81</v>
       </c>
       <c r="L208">
         <v>0.5</v>
       </c>
       <c r="M208">
         <f t="shared" ca="1" si="25"/>
-        <v>0.70430000000000015</v>
+        <v>0.84430000000000027</v>
       </c>
       <c r="N208">
         <f t="shared" ca="1" si="26"/>
-        <v>1.5970521541950111</v>
+        <v>1.9145124716553275</v>
       </c>
       <c r="O208">
         <f t="shared" ca="1" si="27"/>
-        <v>0.49603849000000022</v>
-      </c>
-    </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0.71284249000000044</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>207</v>
       </c>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="D209" s="4">
         <f t="shared" ca="1" si="24"/>
-        <v>68.888800000000003</v>
+        <v>68.243800000000007</v>
       </c>
       <c r="E209" s="1"/>
       <c r="F209" s="1"/>
@@ -10761,26 +10761,26 @@
       </c>
       <c r="J209">
         <f t="shared" ca="1" si="30"/>
-        <v>-0.03</v>
+        <v>-0.71</v>
       </c>
       <c r="K209">
         <f t="shared" ca="1" si="31"/>
-        <v>0.4</v>
+        <v>-0.21</v>
       </c>
       <c r="L209">
         <v>0.5</v>
       </c>
       <c r="M209">
         <f t="shared" ca="1" si="25"/>
-        <v>-0.11119999999999891</v>
+        <v>-0.75619999999999887</v>
       </c>
       <c r="N209">
         <f t="shared" ca="1" si="26"/>
-        <v>-0.16115942028984698</v>
+        <v>-1.0959420289854971</v>
       </c>
       <c r="O209">
         <f t="shared" ca="1" si="27"/>
-        <v>1.2365439999999757E-2</v>
+        <v>0.57183843999999828</v>
       </c>
     </row>
   </sheetData>
